--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-23</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>aletawiksa, al3bor-telecom, amazon_sa</t>
+          <t>aletawiksa, al3bor-telecom</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>50.19 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>204.46 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>8.8 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>28.79 ر.س</t>
+          <t>68.67 ر.س</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>535.95 ر.س</t>
+          <t>470.33 ر.س</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -784,35 +784,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>20.78 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>55.14 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>64.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>المخازن السوداء</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>200.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>المخازن السوداء</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>200.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1863,17 +1863,17 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -2017,17 +2017,17 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2039,44 +2039,44 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
+          <t>باور بانك زولو من انكر، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل USB-C مدمج، حزمة بطارية لايفون 17/16/15، سامسونج S25/S24/S23، ايباد، ايربودز، هواوي، هونر والمزيد (اسود) | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>118.99 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>619.0 ر.س</t>
+          <t>171.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>جوال A7 برو بذاكرة رام 4 جيجا وذاكرة روم 128 جيجا، لون أسود من ريدمي | 800nits Super Sunlight Display, 120Hz High Refresh Rate</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | شحن سريع بي بي اس ثنائي الاتجاه، شاشة رقمية ليد، آمنة للطيران، سعة عالية، يشحن 3 أجهزة في وقت واحد، لأجهزة التابلت / الجوال.</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>419.0 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>جوال HONOR X5c Plus 4G، ذاكرة رام 4GB، ذاكرة ROM 128GB، ثنائي شرائح الاتصال، بطارية 5130mAh، شاشة 6.74 بوصة بتردد 90Hz، كاميرا 50 ميجابكسل، أسود منتصف الليل – إصدار الشرق الأوسط</t>
+          <t>باور بانك من يو جرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب-A مع شحن سريع وحماية للابتوب والهاتف الذكي 3 منافذ | سعة عالية، آمنة للطيران، شحن فائق السرعة 100 واط (2C1A)، شحن ذاتي 65 واط، لأجهزة ماك بوك/سامسونج/ايفون/ايباد</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>453.0 ر.س</t>
+          <t>178.86 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | آمن للطيران، شاشة LED، 5 مخارج و3 مداخل، يشحن 6 أجهزة في وقت واحد، نحيف وصغير الحجم، متوافق مع ايفون واندرويد</t>
+          <t>باور بانك زولو 20,000 مللي أمبير في الساعة و30 واط، شاحن محمول فائق السرعة مع كيبل USB-C مدمج، حزمة بطارية متوافقة مع سلسلة آيفون 17/17 إير/17 برو/17 برو ماكس/16 وجالكسي والمزيد من أنكر، أزرق | شاحن محمول عالي السرعة 20,000 مللي امبير في الساعة لسلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج، أخضر (إصدار المملكة العربية السعودية)</t>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج | شاحن عالي السعة وآمن للاستخدام أثناء الطيران، يدعم الشحن السريع لثلاثة أجهزة، وشاشة عرض رقمية لأجهزة MacBook Air iPad</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>458.0 ر.س</t>
+          <t>178.94 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ | شاشة رقمية ذكية معتمدة من الطيران، شحن فائق السرعة 130 واط، شحن 3 أجهزة في وقت واحد، لأجهزة اللابتوب/ماك بوك/ايفون/سامسونج</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>550.0 ر.س</t>
+          <t>198.83 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>باور بانك محمول 20000 مللي امبير في الساعة 30 واط مع كيبلات مدمجة، بطارية USB C مع شاشة LED لجوالات ايفون وسامسونج وايباد واندرويد من فيسي، مثالي للسفر - اسود</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من بي دي بيست مع كابل مدمج، شحن سريع USB نوع سي 22.5 واط | آمن للطيران، شاشة LED، 5 مخارج و3 مداخل، يشحن 6 أجهزة في وقت واحد، نحيف وصغير الحجم، متوافق مع ايفون واندرويد</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>99.99 ر.س</t>
+          <t>101.0 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
+          <t>باور بانك محمول من بيلكن بمنفذ USB-C بسعة 20000 مللي امبير في الساعة، أسود | شاحن محمول 20000 مللي أمبير، يشحن 3 أجهزة (منفذ USB-C واحد، ومنفذي USB-A)، بقدرة 15 واط، مؤشر LED، بلاستيك معاد تدويره</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>139.99 ر.س</t>
+          <t>78.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>جوال A200 ثنائي شرائح الاتصال بذاكرة رام 3 جيجابايت وسعة 128 جيجابايت وشبكة الجيل الرابع 4G من ايتل، أزرق (Nightly Blue)</t>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>399.0 ر.س</t>
+          <t>139.99 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالاكسي A57 الجيل الخامس 5G نظام أندرويد بسعة تخزين 256 جيجابايت ورام 8 جيجابايت بـ6 ترقيات لنظام التشغيلو شاشة كبيرة وكاميرا 50 ميجابكسل وعمر بطارية طويل، لون أزرق بحري (إصدار السعودية)</t>
+          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها | Detachable USB C Cable, Flight-Safe, Travel Essential, External Phone Battery Pack for iPhone 17 Samsung S26 Honor iPad etc</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>1465.98 ر.س</t>
+          <t>111.14 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>جوال اندرويد 15 بنظام G06 شبكة الجيل الرابع، ذاكرة رام 4+8 جيجابايت وذاكرة داخلية 128 جيجابايت ومعالج MTK هيليو G81 اكستريم وشاشة 6.88 بوصة عالية الدقة بمعدل 120 هرتز من موتورولا، بانتون لوريل اوك</t>
+          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>448.56 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>جوال شاومي ريدمي 15C الذكي 8.256GB، اسود داكن، بطارية 6000mAh | شاشة 120Hz 6.9 انش، تصميم انيق، كاميرا مزدوجة 50MP، شحن سريع 33 واط - اصدار عالمي</t>
+          <t>باور بانك من انكر زولو (اصدار مطور 2026)، شحن سريع 45 واط، بطارية 20,000 مللي امبير في الساعة، كيبل USB نوع سي مزدوج مدمج، منفذ USB نوع سي وايه لايفون 17/16 سيريز وسامسونج اس 25 وهواوي وهونر والمزيد | 20,000mAh Battery Pack with Dual Built-In Cables, USB-C and USB-A Ports, for iPhone 17 / 16 Series, Galaxy, MacBook, and More</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>595.0 ر.س</t>
+          <t>178.8 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>فيجير باور بانك 20000 مللي امبير في الساعة، شاحن محمول رفيع مع كيبلات متعددة مدمجة، بطارية شحن سريع عالية السعة مع شاشة عرض رقمية لايفون وسامسونج والجوالات - اسود</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 8 في 1 مع 4 كابلات USB-C مدمجة، 2 منفذ USB-A ونوع C، شاشة LED للطاقة، مصباح يدوي، بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>95.99 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>جوال ايفون 17 برو ماكس 256 جيجا من ابل: شاشة 6.9 بوصة بتقنية بروموشن وشريحة A19 برو وعمر بطارية استثنائي ونظام كاميرا بروفيوجن وكاميرا أمامية بخاصية سنتر ستيج بلون فضي</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>4999.0 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>جوال ريدمي نوت 15 شبكة الجيل الخامس 5G ثنائي شرائح الاتصال بذاكرة رام 8 جيجابايت وذاكرة داخلية 256 جيجابايت - النسخة العالمية | 108MP Camera,6.77" FHD+ AMOLED Display, IP66 Water &amp; Dust Resistant - Global Version</t>
+          <t>مضخة هواء كهربائية مع 3 فوهات من سكاي تاتش مضخة نفخ مزدوجة الاستخدام للسيارة العائلية سريعة الملء مثالية للأسرة الهوائية والتخييم في الهواء الطلق والقوارب وعوامات السباحة ولعبة الطوافة (أسود)</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>927.55 ر.س</t>
+          <t>23.9 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>دار الأداب الهاربون والباقون</t>
+          <t>مضخة مياه كهربائية محمولة قابلة للشحن بمنفذ USB لعدد 2 عبوة بتصميم محمول للشحن للمكتب والمنزل والتخييم والمطبخ وغيرها سعة 7.5 إلى 19 لتر من سكاي-تاتش أسود</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>98.0 ر.س</t>
+          <t>17.72 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش | Windscreen Front Flyscreen with Mount for Motorbike 5"-7" LED Headlight</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>50.19 ر.س</t>
+          <t>17.72 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>روبوتايم 3 دي بازل هارب</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>206.34 ر.س</t>
+          <t>11.25 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>163.1 ر.س</t>
+          <t>11.17 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>الملاك الهارب</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>52.5 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>ليجو سلسلة 25 - هاربي</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>95.45 ر.س</t>
+          <t>17.72 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>269.0 ر.س</t>
+          <t>21.97 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>تيوامي هارمونيكا هارب هارموك ارمونيكا 24 فتحة فم، مفتاح احترافي سي متعدد الأصوات دياتونيك مع حافظة لموسيقى البوب والجاز الشعبي البلوز</t>
+          <t>مضخة مياه، موزع مياه قابل لإعادة الشحن مع شاحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 ل للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر من لوازم، 12.8 سم × 69 ملم</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>166.85 ر.س</t>
+          <t>12.6 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>330.73 ر.س</t>
+          <t>26.0 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>مضخة مياه كهربائية محمولة مع شحن USB نوع سي، محرك مزدوج وتدفق سريع للمنزل والمكتب والتخييم والسيارة الترفيهية من كوزي تشارم، 19 لتر، أسود</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>289.0 ر.س</t>
+          <t>56.0 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>سرير سفر مع مرتبة مريحة من هاربا، سرير محمول خفيف الوزن لا يتطلب تجميع، عبوة قابلة للطي واللعب للرضع والاطفال الصغار، ساحة لعب صغيرة مع سرير، رمادي | 3-in-1 Playpen, Reinforced Corner Fabric Sleeves, Lightweight Backpack, Breathable Mesh Sides, Zipper Door, Home or Trips Use</t>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>1065.72 ر.س</t>
+          <t>123.06 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>استرو ايه اي ضاغط هواء محمول لنفخ الاطارات 12 فولت تيار مستمر 150 باوند لكل | مضخة كهربائية لإطارات السيارة مع مقياس ضغط الإطارات، منفاخ إطارات بخاصية الإيقاف التلقائي مع محولات صمام ومصباح LED، لون أصفر</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>291.09 ر.س</t>
+          <t>119.98 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>ساعة منبه ران اواي المتدحرجة (الأصلية) من كلوكي، بصوت عال جدا الثقيل (روبوت غرفة النوم للكبار والأطفال) مضحكة، متدحرجة، هاربة، متحركة، قافزة (أزرق)</t>
+          <t>منفاخ هواء من جودتول يدوي مع مضخة و إبرة و فوهة و خرطوم مرن يدوي</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>201.0 ر.س</t>
+          <t>12.54 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>289.0 ر.س</t>
+          <t>88.0 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>ماوس هاربون احترافي باضاءة RGB، اف بي اس/موبا من كورسير - (مستشعر بصري 12000 نقطة لكل بوصة، خفيف الوزن، 6 ازرار قابلة للبرمجة، اضاءة خلفية LED) - لون اسود، USB</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>136.38 ر.س</t>
+          <t>135.15 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>299.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>باور بانك زولو من انكر، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل USB-C مدمج، حزمة بطارية لايفون 17/16/15، سامسونج S25/S24/S23، ايباد، ايربودز، هواوي، هونر والمزيد (اسود) | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك راوتر خارجي MR402 خارجي 4G LTE من ارتشر، واي فاي AC1200Mbps ثنائي النطاق، مقاوم للماء IP65، دعم POE/DC، كات 4 حتى 150 ميجابت في الثانية، تقنية ون ميش، تركيب عمود/حائط، توصيل وتشغيل</t>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>289.0 ر.س</t>
+          <t>78.7 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | آمن للطيران، شاشة LED، 5 مخارج و3 مداخل، يشحن 6 أجهزة في وقت واحد، نحيف وصغير الحجم، متوافق مع ايفون واندرويد</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>82.95 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة | منفذ 1G، PoE+ أو تيار مستمر، محول متضمن، ضمان 5 سنوات، بوابة كابتيف، شبكة، تجوال WPA3، تجربة واي فاي للأعمال</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>327.38 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود | شحن سريع بـ 3 مخرجات آمنة للسفر وحامل جوال وبطارية صغيرة لجوال ايفون 17 و16 وسامسونج اس 25 واس 24 وهونر وغيرها</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>78.0 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>108.0 ر.س</t>
+          <t>118.99 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
+          <t>باور بانك، شاحن محمول صغير 22.5 واط USB C 10000mAh، حزمة بطارية شحن سريع PD 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>48.49 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن TL-POE170S PoE++ (منفذين جيجابت، متوافق مع 802.3af /at/bt، إجمالي الطاقة بقدرة تصل إلى 60 واط، تصميم يثبت على الحائط وسطح المكتب، التوصيل والتشغيل) اسود</t>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت | Ultra-Slim, skin-friendly, ergonomic design, flight-safe, PD 15W Wired Charging, Qi 7.5W Magnetic for iPhone 17/16/15/14/13</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>183.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, high capacity, charges 3 devices at once, for Tablets/Phone</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>226.11 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ | شحن سريع 33 واط (شاومي 33 واط)، كابل USB-C مضفر مدمج (أيضًا كحزام حمل)، شحن 3 أجهزة، حجم صغير</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك راوتر NE200 خارجي 5G مع شريحة اتصال خارجية، سرعة تحميل 5G تصل إلى 4.67Gbps، 4G CAT19 حتى 1.6Gbps، منفذ 2.5GE، يدعم PoE السلبي و802.3af/802.3at، IP66، حامل مرن | إنترنت بدون ألياف في أي مكان. أدخل شريحة الاتصال وانتهى. الرقابة الأبوية. تطبيق تيثر.</t>
+          <t>محول جهد كهربائي 220 فولت إلى 110 فولت من ازوني، محول طاقة للسفر من 220 فولت إلى 110 فولت لأداة فرد الشعر والتلفزيون واللابتوب</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>999.0 ر.س</t>
+          <t>52.24 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>شاحن 17 فولت 1 امبير لمكبر الصوت اللاسلكي بوز ساوند لينك I II III 1 2 3 | محول إمداد الطاقة لـ 301141 404600 414255 306386-101 369946-1300 قابس كابل شحن بديل 17 واط 1 متر</t>
+          <t>محول جهد كهربائي 220 فولت إلى 110 فولت، محول طاقة للسفر 200 واط، محول خافض للجهد الكهربائي 220 فولت إلى 110 فولت لمكواة فرد الشعر وأجهزة التلفزيون واللابتوب من مابروتي</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>61.19 ر.س</t>
+          <t>57.99 ر.س</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>مضخة هواء كهربائية مع 3 فوهات من سكاي تاتش مضخة نفخ مزدوجة الاستخدام للسيارة العائلية سريعة الملء مثالية للأسرة الهوائية والتخييم في الهواء الطلق والقوارب وعوامات السباحة ولعبة الطوافة (أسود)</t>
+          <t>مصدر طاقة يونيفرسال 30 واط بتيار متردد/مستمر مع 8 مقابس تحويل، لـ 3، 4.5، 5، 6، 7.5، 9، 12 فولت، للاستخدامات المنزلية مع شريط LED - اقصى تيار 2000 ميلي امبير</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>23.9 ر.س</t>
+          <t>28.5 ر.س</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>محول مزود طاقة لشريط LED من تيار متردد 100 فولت ~ 240 فولت إلى تيار مستمر 24 فولت 5 امبير 120 واط من موريليان</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>11.0 ر.س</t>
+          <t>35.19 ر.س</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>17.72 ر.س</t>
+          <t>38.29 ر.س</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>11.25 ر.س</t>
+          <t>62.07 ر.س</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>11.17 ر.س</t>
+          <t>75.34 ر.س</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+          <t>جهاز اختبار الخرج من يو ال اتش واي سي، جهاز اختبار جهد خرج المقبس مع عرض جهد 90-250 فولت، جهاز كشف الجهد الكهربائي الاوتوماتيكي للكشف عن قطبية الدارة الكهربائية - HT107E</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>123.06 ر.س</t>
+          <t>48.0 ر.س</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء من إنتكس أوتوماتيكي مع 3 فوهات قابلة للتوصيل كهربائي سلكي</t>
+          <t>محول جهد كهربائي 220 فولت الى 110 فولت، محول طاقة كهربائي، محول سفلي مع حماية من قاطع الدائرة الكهربائية القابلة لإعادة الضبط سهل التوصيل بمقابس الطاقة من هوماركت</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>77.41 ر.س</t>
+          <t>75.69 ر.س</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
+          <t>محول جهد كهربائي من 220 فولت إلى 110 فولت، محول طاقة للسفر لتشغيل لأداة فرد الشعر والتلفزيون واللابتوب من علي اسماعيل</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>21.97 ر.س</t>
+          <t>58.0 ر.س</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+          <t>مكيف هواء 12 فولت تيار مستمر، مكيف سقف قابل للتطبيق على الشاحنات والمركبات الترفيهية والحافلات والحفارات والمخيمات والمركبات الزراعية، مكيف هواء 12 فولت يعمل على البارد والساخن 24 فولت</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>15.66 ر.س</t>
+          <t>1987.09 ر.س</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>محول جهد كهربائي 1500 واط، 110-120 فولت و220-240 فولت، محول تعزيز/باك مع حماية من قاطع الدائرة الكهربائية القابلة لاعادة الضبط، منفذ عالمي، حجم صغير للاستخدام المنزلي</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>17.72 ر.س</t>
+          <t>199.9 ر.س</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+          <t>مبرد هواء اركتيك | للهواء البارد الرطب 5 فولت، 6 واط | مبرد هواء في القطب الشمالي | للحصول على هواء رطب بارد</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>26.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء من جودتول يدوي مع مضخة و إبرة و فوهة و خرطوم مرن يدوي</t>
+          <t>فياجاسافاميدو محول احادي الطور 220 فولت، مخرج تيار متردد 24 فولت 12 فولت، 2 واط، 50 هرتز، لامداد الطاقة والصوت</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>12.54 ر.س</t>
+          <t>32.41 ر.س</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه، موزع مياه قابل لإعادة الشحن مع شاحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 ل للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر من لوازم، 12.8 سم × 69 ملم</t>
+          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>12.6 ر.س</t>
+          <t>599.0 ر.س</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>مبرد سائل لوحدة المعالجة المركزية 240 كور 2 من كولر ماستر، R9|U7|i7 بمضخة G9R مزدوجة ومرآة انفينيتي aRGB وأنبوب 40 سم ورادياتور 240 ملم ومروحة BWM 12 سم AMD رايزن AM5|4 انتل LGA 1851|1700</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>11.79 ر.س</t>
+          <t>297.8 ر.س</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>مضخة بالونات يدوية بحركة مزدوجة، أداة نفخ بالونات مناسبة لصنع الأقواس ونفخ بالونات الرقائق المعدنية والبالونات المزينة بقصاصات ورقية وبالونات الحفلات وكرات اليوغا من جولد ايدج، قطعة واحدة</t>
+          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>8.8 ر.س</t>
+          <t>411.99 ر.س</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
+          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا | 16.7 مليون لون بدون إطار متوافق مع فيسا ، 99% DCI-P3، 120% sRGB، HDMI وDP، شاشة للعمل والألعاب</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>88.0 ر.س</t>
+          <t>519.19 ر.س</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>جيم اون شاشة العاب من سلسلة اي سبورتس GOESP24240IPS، شاشة IPS 61 سم، دقة FHD، معدل تحديث 240Hz، وقت استجابة 0.5 مللي ثانية (ام بي ار تي)، فري سينك/مزامنة تكيفية+ VRR، ضوء ازرق منخفض، اسود</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>135.15 ر.س</t>
+          <t>411.84 ر.س</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>299.0 ر.س</t>
+          <t>285.92 ر.س</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>447.27 ر.س</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>باور بانك زولو من انكر، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل USB-C مدمج، حزمة بطارية لايفون 17/16/15، سامسونج S25/S24/S23، ايباد، ايربودز، هواوي، هونر والمزيد (اسود) | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25 | ألوان 1 مللي ثانية/8 بت/سطوع 350 شمعة لكل متر مربع/بدون إطار/متوافق مع فيسا / HDMI وDP/للمكتب والألعاب</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>422.98 ر.س</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+          <t>مبرد وحدة معالجة مركزية مائي فروزن نوت 240 ابيض ARGB من ثيرمال رايت، مواصفات مبرد وحدة معالجة مركزية 240 ابيض، مراوح PWM مزدوجة محامل S-FDB V2، مناسب لـAMD/AM4 AM5، انتل LGA 1700/1150/1151/1200/2011</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>78.7 ر.س</t>
+          <t>250.0 ر.س</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | آمن للطيران، شاشة LED، 5 مخارج و3 مداخل، يشحن 6 أجهزة في وقت واحد، نحيف وصغير الحجم، متوافق مع ايفون واندرويد</t>
+          <t>Casio Classic Edgy Collection Salmon Pink AQ-240E-4AER Watch</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>278.22 ر.س</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>94.97 ر.س</t>
+          <t>453.69 ر.س</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود | شحن سريع بـ 3 مخرجات آمنة للسفر وحامل جوال وبطارية صغيرة لجوال ايفون 17 و16 وسامسونج اس 25 واس 24 وهونر وغيرها</t>
+          <t>شاشة الألعاب الاحترافية UG25I بحجم 24.5 بوصة - 240Hz/1ms/فري سينك بريميوم - دقة وضوح FHD (1920x1080) - تصميم بدون إطار - تدعم DP و HDMI من زد ايدج | ام بي ار تي 1 مللي ثانية، نسبة تباين 5000:1، 16.7 مليون لون، متوافق مع فيسا، HDMI ودي بي، للألعاب</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>429.97 ر.س</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>مبرد وحدة المعالجة المركزية السائل ايوتا L24 BK 240 ملم AIO مع شاشة رقمية لدرجة الحرارة من اوسيبوس | مضخة ARGB بصرية عائمة، TDP 280 واط، مراوح صامتة بمحمل ديناميكي سائل، دعامة معدنية بالكامل، نظام تبريد مائي لانتل وAMD</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>118.99 ر.س</t>
+          <t>299.99 ر.س</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>باور بانك، شاحن محمول صغير 22.5 واط USB C 10000mAh، حزمة بطارية شحن سريع PD 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد</t>
+          <t>شاشة العاب سامسونج 27 انش، QHD (2560 × 1440)، معدل تحديث 240Hz، وقت استجابة 1 مللي ثانية، ذكي، اسود، كوانتوم دوت، HDR600، LS27BG650EMXUE</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>1259.0 ر.س</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -3650,1049 +3650,15 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت | Ultra-Slim, skin-friendly, ergonomic design, flight-safe, PD 15W Wired Charging, Qi 7.5W Magnetic for iPhone 17/16/15/14/13</t>
+          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>1775.0 ر.س</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | شحن سريع بي بي اس ثنائي الاتجاه، شاشة رقمية ليد، آمنة للطيران، سعة عالية، يشحن 3 أجهزة في وقت واحد، لأجهزة التابلت / الجوال.</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ | شحن سريع 33 واط (شاومي 33 واط)، كابل USB-C مضفر مدمج (أيضًا كحزام حمل)، شحن 3 أجهزة، حجم صغير</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>119.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 220 فولت إلى 110 فولت من ازوني، محول طاقة للسفر من 220 فولت إلى 110 فولت لأداة فرد الشعر والتلفزيون واللابتوب</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>52.24 ر.س</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>مكيف هواء 12 فولت تيار مستمر، مكيف سقف قابل للتطبيق على الشاحنات والمركبات الترفيهية والحافلات والحفارات والمخيمات والمركبات الزراعية، مكيف هواء 12 فولت يعمل على البارد والساخن 24 فولت</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>1987.09 ر.س</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 220 فولت إلى 110 فولت، محول طاقة للسفر 200 واط، محول خافض للجهد الكهربائي 220 فولت إلى 110 فولت لمكواة فرد الشعر وأجهزة التلفزيون واللابتوب من مابروتي</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>57.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>بخاخ فولت مع زجاجة سعة 1 لتر - تصميم خاص (2)</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>40.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>محول مزود طاقة لشريط LED من تيار متردد 100 فولت ~ 240 فولت إلى تيار مستمر 24 فولت 5 امبير 120 واط من موريليان</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>35.19 ر.س</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>موزع مياه ساخن وبارد تحميل سفلي قائم على الارض 220-240 فولت مع ثلاجة من هوميكس - ابيض YLR-LW-2-5-100 باوند</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>498.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>مبرد هواء اركتيك | للهواء البارد الرطب 5 فولت، 6 واط | مبرد هواء في القطب الشمالي | للحصول على هواء رطب بارد</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>49.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>مكيف هواء تي سي ال سبليت ريش ذهبي، 18000 بارد فقط، تبريد قوي عند 60 درجة، خمس سرعات، تبريد سريع، 220 فولت، 50/60 هرتز - بارد فقط - ضمان الوكيل سنتين شامل 10 سنوات على الكمبروسور TAC-18CU/TBF1 من تي سي ال</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>1740.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>62.07 ر.س</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>38.29 ر.س</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>75.34 ر.س</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>سخان سيارة محمول من ابوتو، جهاز ازالة الجليد سريع التسخين 12 فولت مع سرعة مروحة قابلة للتعديل، سخان مروحة سيارة صغير لازالة الضباب، مثالي للسيارات والشاحنات والمركبات في الطقس البارد</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>29.63 ر.س</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>كاربست صنبور نوفو 12 فولت للمنزل المتنقل من كوميت - اسود/كروم، صنبور تخييم مدمج مع مضخة، مثالي لحوض الغسيل والمنزل المتنقل والكارافان</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>75.32 ر.س</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي من 220 فولت إلى 110 فولت، محول طاقة للسفر لتشغيل لأداة فرد الشعر والتلفزيون واللابتوب من علي اسماعيل</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>58.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25 | ألوان 1 مللي ثانية/8 بت/سطوع 350 شمعة لكل متر مربع/بدون إطار/متوافق مع فيسا / HDMI وDP/للمكتب والألعاب</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>422.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>447.27 ر.س</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>جيم اون شاشة العاب من سلسلة اي سبورتس GOESP24240IPS، شاشة IPS 61 سم، دقة FHD، معدل تحديث 240Hz، وقت استجابة 0.5 مللي ثانية (ام بي ار تي)، فري سينك/مزامنة تكيفية+ VRR، ضوء ازرق منخفض، اسود</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>411.84 ر.س</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>370.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>زد-ايدج شاشة العاب منحنية UG27P 27 انش 16:9 1920x1080 240Hz 1ms LED بدون اطار 1ms منفذ عرض ممتاز AMD فري سينك مدمجة HDMI من زد | 8 بت/تباين 3000:1/فري سينك/متوافق مع فيسا/في ايه ليد/اتش دي ام اي ودي بي / شاشة للعمل والألعاب</t>
-        </is>
-      </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>598.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
-        </is>
-      </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>1775.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 32 بوصة FHD 240 هرتز، منحنية 1800R 1080 بكسل (1920 × 1080) فري سينك 100% فضاء لوني ار جي بي، 1 مللي ثانية (GTG) فيسا مناسبة للألعاب الرياضية الإلكترونية والمكتب المنزلي من جاوفولك | FHD(1920x1080) Computer Monitors Fast 1ms(GTG) Freesync 100%sRGB VESA Suitable for e-sports games, office, and home use</t>
-        </is>
-      </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>599.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D155" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب منحنية 24 بوصة 240 هرتز من كيه تي اس، شاشة كمبيوتر منحنية FHD 1500R 1080 بكسل، تباين 3000:1، مزامنة تكيفية، ام بي ار تي1، اتش دي ار مللي ثانية، منفذ عرض اتش دي ام اي، ضوء أزرق منخفض، إمالة | 1500R، تباين 3000:1، مزامنة تكيفية، HDR، MPRT 1 مللي ثانية، منفذ عرض HDMI، ضوء أزرق منخفض، إمالة، حامل فيسا 1080P</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>529.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>MSI مبرد سائل لوحدة المعالجة المركزية كوريليكويد A13 240 من ماج - مبرد سائل لوحدة المعالجة المركزية AIO ARGB - مبرد 240 ملم - متوافق مع LGA 1700/1851 / AM5/AM4 - مراوح مزدوجة 120 ملم ARGB PWM، ابيض</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>263.6 ر.س</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>Casio Classic Edgy Collection Salmon Pink AQ-240E-4AER Watch</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>278.22 ر.س</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>شاشة تي يو اف للألعاب طراز VG27AQM5A مقاس 27 بوصة بدقة FHD (1920×1080) وتردد 240 هرتز، لوحة IPS فاست بزمن استجابة 0.3 ميلي ثانية مع تقنيات جي سينك وفري سينك وألوان ار جي بي وديسبلاي ويدجيت من اسوس | 240 هرتز، مزامنة ELMB، 0.3 مللي ثانية، 99% sRGB، ألعاب الذكاء الاصطناعي، متوافقة مع جي سينك، مركز عرض ويدجيت</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>800.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>KTC 32 inch 240Hz Curved Gaming Monitor, 1080P PC Monitor, Black H32S17F | 1500R 1080P 125% sRGB 1ms, Freesync/G-sync HDR10,HDMI/DP/USB Ports VESA,Tilt Adjustable,Xbox PS5 Switch,</t>
-        </is>
-      </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>859.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>ديل شاشة العاب 24 - SE2426HG، FHD (1920×1080)، 240Hz، تقنية IPS سريعة، 0.5 مللي ثانية، AMD فري سينك بريميوم، 99% sRGB، HDR10، فيسا (100×100 ملم)، منفذ عرض، 2 HDMI، ضمان 3 سنوات، اسود</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>489.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>MSI شاشة العاب 274CF X24 من ماج 27 انش 1920 × 1080 (FHD)، 240 هرتز، AMD ادابتيف سينك، HDR جاهز، HDMI، منفذ VGA، حامل فيسا وامالة، اطار رفيع رباعي الجوانب، 0.5 مللي ثانية، اسود</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>578.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="20" customHeight="1">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>38.39 ر.س</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج | شحن سريع لأجهزة ماك بوك واللاب توب، اشحن 3 أجهزة في وقت واحد، حماية ذكية للسلامة، للرحلات الطويلة على الطريق</t>
-        </is>
-      </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>آلة تعبئة تلقائية مع 3 منافذ 130 واط موديل EC705 من يوجرين</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>119.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة | شحن سريع من النوع سي لايفون 17/16/15/14، سامسونج، شاومي، موتورولا، ايربودز وغيرها</t>
-        </is>
-      </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من إينيو بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج S23 وS22 وآيباد، منفذين، 30 واط، شحن سريع وتصميم مدمج | معدن بالكامل، حماية ذكية للسلامة، شاحن سيارة صغير من النوع سي لموبايل ايفون 17 16 برو ماكس وسامسونج اس 26 واس 25 وهواوي هونر</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>35.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة | 3 منافذ لجميع أجهزة USB-C/A، لجميع المركبات 12-24 فولت، تصميم خفيف الوزن، جاهز للسفر، حماية ذكية للسلامة</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>20.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة | منفذان لجميع أجهزة USB-C/A، لجميع المركبات 12-24 فولت، مثالي للتنقل اليومي، حماية ذكية للسلامة</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>39.18 ر.س</t>
-        </is>
-      </c>
-      <c r="D171" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة | منفذان لجميع أجهزة USB-C/A، لجميع المركبات 12-24 فولت، تصميم خفيف الوزن، جاهز للسفر، حماية ذكية للسلامة</t>
-        </is>
-      </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>59.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D172" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="20" customHeight="1">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب | يعمل بسلاسة مع ايفون وسامسونج وماك بوك وجميع أجهزة USB-C/A، يشحن 3 أجهزة في وقت واحد، للرحلات والسفر</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>75.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب | ولاعة سجائر مع كيبل قابل للسحب 65 واط، منافذ شحن USB نوع C وUSB A، عرض الجهد، لاجهزة ايفون/اندرويد/ايباد/لاب توب</t>
-        </is>
-      </c>
-      <c r="C174" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="20" customHeight="1">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>35.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D175" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة | يعمل بسلاسة مع ايفون وسامسونج وماك بوك وجميع أجهزة USB-C/A، يشحن جهازين في وقت واحد، للتنقل اليومي</t>
-        </is>
-      </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>68.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XZM بمنفذ USB و USB-C متوافق مع آيفون بمنفذين بقدرة 60 واط مع شحن سريع وتقنية ذكية وإضاءة RGB</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>24.69 ر.س</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-24</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>68.67 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,35 +749,35 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>35.19 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>470.33 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2036,1634 +2036,6 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك زولو من انكر، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل USB-C مدمج، حزمة بطارية لايفون 17/16/15، سامسونج S25/S24/S23، ايباد، ايربودز، هواوي، هونر والمزيد (اسود) | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>118.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>171.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | شحن سريع بي بي اس ثنائي الاتجاه، شاشة رقمية ليد، آمنة للطيران، سعة عالية، يشحن 3 أجهزة في وقت واحد، لأجهزة التابلت / الجوال.</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب-A مع شحن سريع وحماية للابتوب والهاتف الذكي 3 منافذ | سعة عالية، آمنة للطيران، شحن فائق السرعة 100 واط (2C1A)، شحن ذاتي 65 واط، لأجهزة ماك بوك/سامسونج/ايفون/ايباد</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>178.86 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك زولو 20,000 مللي أمبير في الساعة و30 واط، شاحن محمول فائق السرعة مع كيبل USB-C مدمج، حزمة بطارية متوافقة مع سلسلة آيفون 17/17 إير/17 برو/17 برو ماكس/16 وجالكسي والمزيد من أنكر، أزرق | شاحن محمول عالي السرعة 20,000 مللي امبير في الساعة لسلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج | شاحن عالي السعة وآمن للاستخدام أثناء الطيران، يدعم الشحن السريع لثلاثة أجهزة، وشاشة عرض رقمية لأجهزة MacBook Air iPad</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>178.94 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ | شاشة رقمية ذكية معتمدة من الطيران، شحن فائق السرعة 130 واط، شحن 3 أجهزة في وقت واحد، لأجهزة اللابتوب/ماك بوك/ايفون/سامسونج</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>198.83 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من بي دي بيست مع كابل مدمج، شحن سريع USB نوع سي 22.5 واط | آمن للطيران، شاشة LED، 5 مخارج و3 مداخل، يشحن 6 أجهزة في وقت واحد، نحيف وصغير الحجم، متوافق مع ايفون واندرويد</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>101.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك محمول من بيلكن بمنفذ USB-C بسعة 20000 مللي امبير في الساعة، أسود | شاحن محمول 20000 مللي أمبير، يشحن 3 أجهزة (منفذ USB-C واحد، ومنفذي USB-A)، بقدرة 15 واط، مؤشر LED، بلاستيك معاد تدويره</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>78.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>139.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها | Detachable USB C Cable, Flight-Safe, Travel Essential, External Phone Battery Pack for iPhone 17 Samsung S26 Honor iPad etc</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>111.14 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من انكر زولو (اصدار مطور 2026)، شحن سريع 45 واط، بطارية 20,000 مللي امبير في الساعة، كيبل USB نوع سي مزدوج مدمج، منفذ USB نوع سي وايه لايفون 17/16 سيريز وسامسونج اس 25 وهواوي وهونر والمزيد | 20,000mAh Battery Pack with Dual Built-In Cables, USB-C and USB-A Ports, for iPhone 17 / 16 Series, Galaxy, MacBook, and More</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>178.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 8 في 1 مع 4 كابلات USB-C مدمجة، 2 منفذ USB-A ونوع C، شاشة LED للطاقة، مصباح يدوي، بطارية عالية السعة للجوال والتابلت</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>99.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>مضخة هواء كهربائية مع 3 فوهات من سكاي تاتش مضخة نفخ مزدوجة الاستخدام للسيارة العائلية سريعة الملء مثالية للأسرة الهوائية والتخييم في الهواء الطلق والقوارب وعوامات السباحة ولعبة الطوافة (أسود)</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>23.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية محمولة قابلة للشحن بمنفذ USB لعدد 2 عبوة بتصميم محمول للشحن للمكتب والمنزل والتخييم والمطبخ وغيرها سعة 7.5 إلى 19 لتر من سكاي-تاتش أسود</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>17.72 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>17.72 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>11.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>11.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>15.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>17.72 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>21.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه، موزع مياه قابل لإعادة الشحن مع شاحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 ل للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر من لوازم، 12.8 سم × 69 ملم</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>12.6 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>26.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية محمولة مع شحن USB نوع سي، محرك مزدوج وتدفق سريع للمنزل والمكتب والتخييم والسيارة الترفيهية من كوزي تشارم، 19 لتر، أسود</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>56.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>123.06 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>استرو ايه اي ضاغط هواء محمول لنفخ الاطارات 12 فولت تيار مستمر 150 باوند لكل | مضخة كهربائية لإطارات السيارة مع مقياس ضغط الإطارات، منفاخ إطارات بخاصية الإيقاف التلقائي مع محولات صمام ومصباح LED، لون أصفر</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>119.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>منفاخ هواء من جودتول يدوي مع مضخة و إبرة و فوهة و خرطوم مرن يدوي</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>12.54 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>135.15 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك زولو من انكر، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل USB-C مدمج، حزمة بطارية لايفون 17/16/15، سامسونج S25/S24/S23، ايباد، ايربودز، هواوي، هونر والمزيد (اسود) | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>78.7 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | آمن للطيران، شاشة LED، 5 مخارج و3 مداخل، يشحن 6 أجهزة في وقت واحد، نحيف وصغير الحجم، متوافق مع ايفون واندرويد</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>82.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>94.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود | شحن سريع بـ 3 مخرجات آمنة للسفر وحامل جوال وبطارية صغيرة لجوال ايفون 17 و16 وسامسونج اس 25 واس 24 وهونر وغيرها</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>118.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك، شاحن محمول صغير 22.5 واط USB C 10000mAh، حزمة بطارية شحن سريع PD 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت | Ultra-Slim, skin-friendly, ergonomic design, flight-safe, PD 15W Wired Charging, Qi 7.5W Magnetic for iPhone 17/16/15/14/13</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, high capacity, charges 3 devices at once, for Tablets/Phone</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ | شحن سريع 33 واط (شاومي 33 واط)، كابل USB-C مضفر مدمج (أيضًا كحزام حمل)، شحن 3 أجهزة، حجم صغير</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>119.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 220 فولت إلى 110 فولت من ازوني، محول طاقة للسفر من 220 فولت إلى 110 فولت لأداة فرد الشعر والتلفزيون واللابتوب</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>52.24 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 220 فولت إلى 110 فولت، محول طاقة للسفر 200 واط، محول خافض للجهد الكهربائي 220 فولت إلى 110 فولت لمكواة فرد الشعر وأجهزة التلفزيون واللابتوب من مابروتي</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>57.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>مصدر طاقة يونيفرسال 30 واط بتيار متردد/مستمر مع 8 مقابس تحويل، لـ 3، 4.5، 5، 6، 7.5، 9، 12 فولت، للاستخدامات المنزلية مع شريط LED - اقصى تيار 2000 ميلي امبير</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>28.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>محول مزود طاقة لشريط LED من تيار متردد 100 فولت ~ 240 فولت إلى تيار مستمر 24 فولت 5 امبير 120 واط من موريليان</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>35.19 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>38.29 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>62.07 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>75.34 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار الخرج من يو ال اتش واي سي، جهاز اختبار جهد خرج المقبس مع عرض جهد 90-250 فولت، جهاز كشف الجهد الكهربائي الاوتوماتيكي للكشف عن قطبية الدارة الكهربائية - HT107E</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>48.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 220 فولت الى 110 فولت، محول طاقة كهربائي، محول سفلي مع حماية من قاطع الدائرة الكهربائية القابلة لإعادة الضبط سهل التوصيل بمقابس الطاقة من هوماركت</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>75.69 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي من 220 فولت إلى 110 فولت، محول طاقة للسفر لتشغيل لأداة فرد الشعر والتلفزيون واللابتوب من علي اسماعيل</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>58.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>مكيف هواء 12 فولت تيار مستمر، مكيف سقف قابل للتطبيق على الشاحنات والمركبات الترفيهية والحافلات والحفارات والمخيمات والمركبات الزراعية، مكيف هواء 12 فولت يعمل على البارد والساخن 24 فولت</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>1987.09 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 1500 واط، 110-120 فولت و220-240 فولت، محول تعزيز/باك مع حماية من قاطع الدائرة الكهربائية القابلة لاعادة الضبط، منفذ عالمي، حجم صغير للاستخدام المنزلي</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>199.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>مبرد هواء اركتيك | للهواء البارد الرطب 5 فولت، 6 واط | مبرد هواء في القطب الشمالي | للحصول على هواء رطب بارد</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>49.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>فياجاسافاميدو محول احادي الطور 220 فولت، مخرج تيار متردد 24 فولت 12 فولت، 2 واط، 50 هرتز، لامداد الطاقة والصوت</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>32.41 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل لوحدة المعالجة المركزية 240 كور 2 من كولر ماستر، R9|U7|i7 بمضخة G9R مزدوجة ومرآة انفينيتي aRGB وأنبوب 40 سم ورادياتور 240 ملم ومروحة BWM 12 سم AMD رايزن AM5|4 انتل LGA 1851|1700</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>297.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>411.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا | 16.7 مليون لون بدون إطار متوافق مع فيسا ، 99% DCI-P3، 120% sRGB، HDMI وDP، شاشة للعمل والألعاب</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>519.19 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>جيم اون شاشة العاب من سلسلة اي سبورتس GOESP24240IPS، شاشة IPS 61 سم، دقة FHD، معدل تحديث 240Hz، وقت استجابة 0.5 مللي ثانية (ام بي ار تي)، فري سينك/مزامنة تكيفية+ VRR، ضوء ازرق منخفض، اسود</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>411.84 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>285.92 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>447.27 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25 | ألوان 1 مللي ثانية/8 بت/سطوع 350 شمعة لكل متر مربع/بدون إطار/متوافق مع فيسا / HDMI وDP/للمكتب والألعاب</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>422.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة معالجة مركزية مائي فروزن نوت 240 ابيض ARGB من ثيرمال رايت، مواصفات مبرد وحدة معالجة مركزية 240 ابيض، مراوح PWM مزدوجة محامل S-FDB V2، مناسب لـAMD/AM4 AM5، انتل LGA 1700/1150/1151/1200/2011</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>250.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>Casio Classic Edgy Collection Salmon Pink AQ-240E-4AER Watch</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>278.22 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>453.69 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>شاشة الألعاب الاحترافية UG25I بحجم 24.5 بوصة - 240Hz/1ms/فري سينك بريميوم - دقة وضوح FHD (1920x1080) - تصميم بدون إطار - تدعم DP و HDMI من زد ايدج | ام بي ار تي 1 مللي ثانية، نسبة تباين 5000:1، 16.7 مليون لون، متوافق مع فيسا، HDMI ودي بي، للألعاب</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>429.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة المعالجة المركزية السائل ايوتا L24 BK 240 ملم AIO مع شاشة رقمية لدرجة الحرارة من اوسيبوس | مضخة ARGB بصرية عائمة، TDP 280 واط، مراوح صامتة بمحمل ديناميكي سائل، دعامة معدنية بالكامل، نظام تبريد مائي لانتل وAMD</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>299.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب سامسونج 27 انش، QHD (2560 × 1440)، معدل تحديث 240Hz، وقت استجابة 1 مللي ثانية، ذكي، اسود، كوانتوم دوت، HDR600، LS27BG650EMXUE</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>1259.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>1775.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-25</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -679,35 +679,35 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,974 @@
         </is>
       </c>
     </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>491.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج، أخضر (إصدار المملكة العربية السعودية)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>449.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>423.11 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>جوال ريدمي A7 برو بذاكرة رام 4 جيجا وسعة تخزين 128 جيجا، لون أخضر (Palm Green) | 800nits Super Sunlight Display, 120Hz High Refresh Rate</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>419.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك محمول 20000 مللي امبير في الساعة 30 واط مع كيبلات مدمجة، بطارية USB C مع شاشة LED لجوالات ايفون وسامسونج وايباد واندرويد من فيسي، مثالي للسفر - اسود</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>89.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>جوال A200 ثنائي شرائح الاتصال بذاكرة رام 3 جيجابايت وسعة 128 جيجابايت وشبكة الجيل الرابع 4G من ايتل، أزرق (Nightly Blue)</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>628.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>جوال سامسونج جالاكسي A57 الجيل الخامس 5G نظام أندرويد بسعة تخزين 256 جيجابايت ورام 8 جيجابايت بـ6 ترقيات لنظام التشغيلو شاشة كبيرة وكاميرا 50 ميجابكسل وعمر بطارية طويل، لون أزرق بحري (إصدار السعودية)</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>1335.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>139.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>جوال ايفون 17 برو ماكس 256 جيجا من ابل: شاشة 6.9 بوصة بتقنية بروموشن وشريحة A19 برو وعمر بطارية استثنائي ونظام كاميرا بروفيوجن وكاميرا أمامية بخاصية سنتر ستيج بلون فضي</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>5086.28 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>جوال شاومي ريدمي 15C الذكي 8.256GB، اسود داكن، بطارية 6000mAh | شاشة 120Hz 6.9 انش، تصميم انيق، كاميرا مزدوجة 50MP، شحن سريع 33 واط - اصدار عالمي</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>595.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>جوال ريدمي نوت 15 شبكة الجيل الخامس 5G ثنائي شرائح الاتصال بذاكرة رام 8 جيجابايت وذاكرة داخلية 256 جيجابايت - النسخة العالمية | 108MP Camera,6.77" FHD+ AMOLED Display, IP66 Water &amp; Dust Resistant - Global Version</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>927.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>جوال نوكيا 106 NENA1 ثنائي شرائح الاتصال، ذاكرة رام 48 ميجابايت + ذاكرة روم 128 ميجابايت، (1.8 بوصة) (شبكة الجيل الثاني 2G) - (لون فحمي)، TA-1564 DS</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>112.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>جوال موتورولا G06 4G، ذاكرة وصول عشوائية 4+8 جيجابايت، وذاكرة داخلية 128 جيجابايت، ومعالج ام تي كيه هيليو G81 اكستريم، وشاشة 6.88 بوصة فائقة الدقة 120 هرتز، نظام اندرويد 15، لون بانتون تابيستري</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>448.65 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>135.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>295.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك زولو من انكر، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل USB-C مدمج، حزمة بطارية لايفون 17/16/15، سامسونج S25/S24/S23، ايباد، ايربودز، هواوي، هونر والمزيد (اسود)</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>94.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>78.7 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود | 3-Output Fast Charging, Flight-Safe for Travel, Phone Holder, Mini Battery Pack for iPhone 17 16 Samsung S25 S24 Honor etc</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>118.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, high capacity, charges 3 devices at once, for Tablets/Phone</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>138.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك، شاحن محمول صغير 22.5 واط USB C 10000mAh، حزمة بطارية شحن سريع PD 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت | Ultra-Slim, skin-friendly, ergonomic design, flight-safe, PD 15W Wired Charging, Qi 7.5W Magnetic for iPhone 17/16/15/14/13</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | آمن للطيران، شاشة LED، 5 مخارج و3 مداخل، يشحن 6 أجهزة في وقت واحد، نحيف وصغير الحجم، متوافق مع ايفون واندرويد</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>298.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ميت باد 11.5 S مع شاشة بيبر ميت فائقة الوضوح وسعة 12جيجابايت و256 جيجابايت ببطارية 8800 ميلي امبير في الساعة وشحن فائق 40 واط وكيبورد قابل للفصل من هواوي ميت، أخضر</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>1799.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>جهاز ريدمي باد 2 بذاكرة رام 4 جيجا وذاكرة تخزين 128 جيجا، لون رمادي جرافيت</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>649.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في | دقة 2.8 كيه، ضوء 509 غرام، شحن فائق 66 واط، قلم ام الجيل الثالث + كيبورد مغناطيسي + ماوس + عبوة عناية الكل في واحد</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>3499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>تابلت شاومي باد 7 8 + 128 بلون أسود + قلم</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>1802.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>روم تيك بطارية سيموس لجهاز لينوفو ثينك باد T430 T450S T460 T430I T430S - بطارية احتياطية للابتوب بيوس ار تي سي 3 فولت CR2032 T430 CMOS للوحة الام للكمبيوتر مع كيبل 2 سلك بدبوسين (عبوة واحدة)</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>74.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>اونر تابلت باد 9 12.1 انش 8GB/256GB 2 5K 12.1 انش 2.5K 120Hz 8300mAh واي فاي 5 بلاتا</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>1868.82 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3 سناب دراجون® 8 ايليت معدل تحديث 144 هرتز مع تقنية واي فاي (لون فضي مصنفر، 16+ 512 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>5385.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت ريدمي باد 2 6 جيجابايت + 128 جيجابايت شاشة 11 بوصة، رمادي (الشاحن متضمن)</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>985.46 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ريدمي باد 2 الجيل الرابع 4G وذاكرة رام 8 جيجابايت وروم 256 جيجابايت، بشاشة 11 بوصة FHD+ 90 هرتز وكاميرا 8MP وبطارية 9000 مللي امبير في الساعة، مكبرات صوت رباعية من شاومي، رمادي (Graphite)</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>1273.36 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا سناب دراغون 7s الجيل الرابع شاشة 12.1 انش 2.5 كيه 120 هرتز بطارية 12000mAh + شحن سريع 33 واط كاميرا مزدوجة 8MP ازرق (مع الشاحن متضمن)</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>1421.43 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB | دقة 2.8K، وزن 509 جم، شحن فائق السرعة 66 واط، قلم M-بنسل من الجيل الثالث + لوحة مفاتيح مغناطيسية + ماوس + باقة كير متكاملة</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>3599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت T5 10 2G 16 LTE</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>734.07 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>سامسونج تابلت جالكسي تاب اس 10 اف اي بلس 13.1 انش 128GB واي فاي اندرويد بشاشة كبيرة وعمر بطارية طويل ومعالج اكسينوس 1580، مقاوم للماء بتصنيف IP68، تحديث 90Hz، قلم اس لتدوين الملاحظات، اصدار امريكي، ازرق</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>2597.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>ايه بيوتي جراب دوار لهاتف هواوي ميت باد 11.5 اس 2024 فضي | مع حامل قلم، حامل دوار 360 درجة، غطاء خلفي شفاف مضاد للصدمات، خاصية الاستيقاظ/النوم التلقائي</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>36.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-26</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -679,35 +679,35 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -944,7 +944,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>عروض العطاوي</t>
+          <t>عروض الكفرات</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>عروض العطاوي</t>
+          <t>عروض الكفرات</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -2033,974 +2033,6 @@
       <c r="D56" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>549.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>491.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج، أخضر (إصدار المملكة العربية السعودية)</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>449.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>423.11 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>جوال ريدمي A7 برو بذاكرة رام 4 جيجا وسعة تخزين 128 جيجا، لون أخضر (Palm Green) | 800nits Super Sunlight Display, 120Hz High Refresh Rate</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>419.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك محمول 20000 مللي امبير في الساعة 30 واط مع كيبلات مدمجة، بطارية USB C مع شاشة LED لجوالات ايفون وسامسونج وايباد واندرويد من فيسي، مثالي للسفر - اسود</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>89.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>جوال A200 ثنائي شرائح الاتصال بذاكرة رام 3 جيجابايت وسعة 128 جيجابايت وشبكة الجيل الرابع 4G من ايتل، أزرق (Nightly Blue)</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>399.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>628.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>جوال سامسونج جالاكسي A57 الجيل الخامس 5G نظام أندرويد بسعة تخزين 256 جيجابايت ورام 8 جيجابايت بـ6 ترقيات لنظام التشغيلو شاشة كبيرة وكاميرا 50 ميجابكسل وعمر بطارية طويل، لون أزرق بحري (إصدار السعودية)</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>1335.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>139.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>جوال ايفون 17 برو ماكس 256 جيجا من ابل: شاشة 6.9 بوصة بتقنية بروموشن وشريحة A19 برو وعمر بطارية استثنائي ونظام كاميرا بروفيوجن وكاميرا أمامية بخاصية سنتر ستيج بلون فضي</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>5086.28 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>جوال شاومي ريدمي 15C الذكي 8.256GB، اسود داكن، بطارية 6000mAh | شاشة 120Hz 6.9 انش، تصميم انيق، كاميرا مزدوجة 50MP، شحن سريع 33 واط - اصدار عالمي</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>595.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>جوال ريدمي نوت 15 شبكة الجيل الخامس 5G ثنائي شرائح الاتصال بذاكرة رام 8 جيجابايت وذاكرة داخلية 256 جيجابايت - النسخة العالمية | 108MP Camera,6.77" FHD+ AMOLED Display, IP66 Water &amp; Dust Resistant - Global Version</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>927.55 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>جوال نوكيا 106 NENA1 ثنائي شرائح الاتصال، ذاكرة رام 48 ميجابايت + ذاكرة روم 128 ميجابايت، (1.8 بوصة) (شبكة الجيل الثاني 2G) - (لون فحمي)، TA-1564 DS</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>112.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>جوال موتورولا G06 4G، ذاكرة وصول عشوائية 4+8 جيجابايت، وذاكرة داخلية 128 جيجابايت، ومعالج ام تي كيه هيليو G81 اكستريم، وشاشة 6.88 بوصة فائقة الدقة 120 هرتز، نظام اندرويد 15، لون بانتون تابيستري</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>448.65 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>135.15 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>295.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك زولو من انكر، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل USB-C مدمج، حزمة بطارية لايفون 17/16/15، سامسونج S25/S24/S23، ايباد، ايربودز، هواوي، هونر والمزيد (اسود)</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>94.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>78.7 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود | 3-Output Fast Charging, Flight-Safe for Travel, Phone Holder, Mini Battery Pack for iPhone 17 16 Samsung S25 S24 Honor etc</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>118.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, high capacity, charges 3 devices at once, for Tablets/Phone</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك، شاحن محمول صغير 22.5 واط USB C 10000mAh، حزمة بطارية شحن سريع PD 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت | Ultra-Slim, skin-friendly, ergonomic design, flight-safe, PD 15W Wired Charging, Qi 7.5W Magnetic for iPhone 17/16/15/14/13</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | آمن للطيران، شاشة LED، 5 مخارج و3 مداخل، يشحن 6 أجهزة في وقت واحد، نحيف وصغير الحجم، متوافق مع ايفون واندرويد</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>298.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ميت باد 11.5 S مع شاشة بيبر ميت فائقة الوضوح وسعة 12جيجابايت و256 جيجابايت ببطارية 8800 ميلي امبير في الساعة وشحن فائق 40 واط وكيبورد قابل للفصل من هواوي ميت، أخضر</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>1799.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>جهاز ريدمي باد 2 بذاكرة رام 4 جيجا وذاكرة تخزين 128 جيجا، لون رمادي جرافيت</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>649.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في | دقة 2.8 كيه، ضوء 509 غرام، شحن فائق 66 واط، قلم ام الجيل الثالث + كيبورد مغناطيسي + ماوس + عبوة عناية الكل في واحد</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>3499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>تابلت شاومي باد 7 8 + 128 بلون أسود + قلم</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>1802.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>روم تيك بطارية سيموس لجهاز لينوفو ثينك باد T430 T450S T460 T430I T430S - بطارية احتياطية للابتوب بيوس ار تي سي 3 فولت CR2032 T430 CMOS للوحة الام للكمبيوتر مع كيبل 2 سلك بدبوسين (عبوة واحدة)</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>74.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>اونر تابلت باد 9 12.1 انش 8GB/256GB 2 5K 12.1 انش 2.5K 120Hz 8300mAh واي فاي 5 بلاتا</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>1868.82 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ون بلس باد 3 سناب دراجون® 8 ايليت معدل تحديث 144 هرتز مع تقنية واي فاي (لون فضي مصنفر، 16+ 512 جيجابايت)</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>5385.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 6 جيجابايت + 128 جيجابايت شاشة 11 بوصة، رمادي (الشاحن متضمن)</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>985.46 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ريدمي باد 2 الجيل الرابع 4G وذاكرة رام 8 جيجابايت وروم 256 جيجابايت، بشاشة 11 بوصة FHD+ 90 هرتز وكاميرا 8MP وبطارية 9000 مللي امبير في الساعة، مكبرات صوت رباعية من شاومي، رمادي (Graphite)</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>1273.36 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا سناب دراغون 7s الجيل الرابع شاشة 12.1 انش 2.5 كيه 120 هرتز بطارية 12000mAh + شحن سريع 33 واط كاميرا مزدوجة 8MP ازرق (مع الشاحن متضمن)</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>1421.43 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB | دقة 2.8K، وزن 509 جم، شحن فائق السرعة 66 واط، قلم M-بنسل من الجيل الثالث + لوحة مفاتيح مغناطيسية + ماوس + باقة كير متكاملة</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>3599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت T5 10 2G 16 LTE</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>734.07 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>سامسونج تابلت جالكسي تاب اس 10 اف اي بلس 13.1 انش 128GB واي فاي اندرويد بشاشة كبيرة وعمر بطارية طويل ومعالج اكسينوس 1580، مقاوم للماء بتصنيف IP68، تحديث 90Hz، قلم اس لتدوين الملاحظات، اصدار امريكي، ازرق</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>2597.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>ايه بيوتي جراب دوار لهاتف هواوي ميت باد 11.5 اس 2024 فضي | مع حامل قلم، حامل دوار 360 درجة، غطاء خلفي شفاف مضاد للصدمات، خاصية الاستيقاظ/النوم التلقائي</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>36.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-27</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -644,35 +644,35 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>56.14 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,70 +749,70 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>553.78 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>64.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>60.98 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1819,17 +1819,17 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1973,17 +1973,17 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -1995,44 +1995,1980 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>118.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>171.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك زولو 20,000 مللي أمبير في الساعة و30 واط، شاحن محمول فائق السرعة مع كيبل USB-C مدمج، حزمة بطارية متوافقة مع سلسلة آيفون 17/17 إير/17 برو/17 برو ماكس/16 وجالكسي والمزيد من أنكر، أزرق</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب-A مع شحن سريع وحماية للابتوب والهاتف الذكي 3 منافذ | high-capacity, flight-safe, ultra-fast 100W charging(2C1A), 65W self-charging, for MacBook/Samsung/iPhone/iPad</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>178.86 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, high capacity, charges 3 devices at once, for Tablets/Phone</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>138.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج | شاحن عالي السعة وآمن للاستخدام أثناء الطيران، يدعم الشحن السريع لثلاثة أجهزة، وشاشة عرض رقمية لأجهزة MacBook Air iPad</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>178.94 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>139.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000 | حزمة بطارية 20,000 مللي أمبير في الساعة مع كابلات مدمجة مزدوجة، منافذ USB-C وUSB-A لسلسلة ايفون 17 / 16 وجالكسي وماك بوك</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>178.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها | Detachable USB C Cable, Flight-Safe, Travel Essential, External Phone Battery Pack for iPhone 17 Samsung S26 Honor iPad etc</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>111.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ | Flight-Approved, smart digital display, 130W ultra-fast charging, charge 3 devices at once, for Laptop/MacBook/iPhone/Samsung</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>198.83 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>شاومي باور بانك 67 واط 20,000 مللي امبير في الساعة مع كابل مدمج - شاحن سريع محمول بيج داكن</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>119.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن جيجابت PoE 802.3at/af | محول غير PoE الى PoE | لوازم PoE (15.4 واط) او PoE+ (30 واط) | التوصيل والتشغيل | سطح المكتب/الحائط | مسافة تصل الى 100 متر (PoE160S)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>46.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>46.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة | منفذ 1G، PoE+ أو تيار مستمر، محول متضمن، ضمان 5 سنوات، بوابة كابتيف، شبكة، تجوال WPA3، تجربة واي فاي للأعمال</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>327.26 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن TL-POE170S PoE++ (منفذين جيجابت، متوافق مع 802.3af /at/bt، إجمالي الطاقة بقدرة تصل إلى 60 واط، تصميم يثبت على الحائط وسطح المكتب، التوصيل والتشغيل) اسود</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>183.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك راوتر خارجي MR402 خارجي 4G LTE من ارتشر، واي فاي AC1200Mbps ثنائي النطاق، مقاوم للماء IP65، دعم POE/DC، كات 4 حتى 150 ميجابت في الثانية، تقنية ون ميش، تركيب عمود/حائط، توصيل وتشغيل</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>289.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>221.61 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>48.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك WLAN Access P. 300mb في الهواء الطلق, CPE210 | وصلة لاسلكية طويلة المدى. هوائي اتجاهي عالي الكسب. مثالية للاستخدام في الهواء الطلق. نقل من نقطة إلى نقطة.</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>220.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>مضخة هواء كهربائية مع 3 فوهات من سكاي تاتش مضخة نفخ مزدوجة الاستخدام للسيارة العائلية سريعة الملء مثالية للأسرة الهوائية والتخييم في الهواء الطلق والقوارب وعوامات السباحة ولعبة الطوافة (أسود)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>23.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>17.72 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>11.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>21.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>11.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه، موزع مياه قابل لإعادة الشحن مع شاحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 ل للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر من لوازم، 12.8 سم × 69 ملم</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>12.6 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>17.72 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>106.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>منفاخ هواء من إنتكس أوتوماتيكي مع 3 فوهات قابلة للتوصيل كهربائي سلكي</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>77.23 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>26.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>15.66 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>مضخة موزع مياه من لوازم بتصميم حديث، براد ماء بشكل مستدير، مصنوع من ستانلس ستيل وبلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>15.84 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>استرو ايه اي ضاغط هواء محمول لنفخ الاطارات 12 فولت تيار مستمر 150 باوند لكل | مضخة كهربائية لإطارات السيارة مع مقياس ضغط الإطارات، منفاخ إطارات بخاصية الإيقاف التلقائي مع محولات صمام ومصباح LED، لون أصفر</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>119.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>منفاخ هواء يدوي مريح محمول بمقبض من الفولاذ على شكل حرف T وخرطوم نفخ وصمام متوافق وألوان مختلطة لإطارات الدراجات والكرات ومعدات التخييم</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>12.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>1779.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في | دقة 2.8 كيه، ضوء 509 غرام، شحن فائق 66 واط، قلم ام الجيل الثالث + كيبورد مغناطيسي + ماوس + عبوة عناية الكل في واحد</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>3499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت ريدمي باد 2 مي، 6GB + 128GB، رمادي، شاشة 11 انش 2.5K 90Hz بطارية 9000mAh، ام تي كيه هيليو G100-Ultra 8MP مع مكبرات صوت رباعية</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>984.04 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>اونر تابلت باد 9 12.1 انش 8GB/256GB 2 5K 12.1 انش 2.5K 120Hz 8300mAh واي فاي 5 بلاتا</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>1868.82 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB | دقة 2.8K، وزن 509 جم، شحن فائق السرعة 66 واط، قلم M-بنسل من الجيل الثالث + لوحة مفاتيح مغناطيسية + ماوس + باقة كير متكاملة</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>3599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3 سناب دراجون® 8 ايليت معدل تحديث 144 هرتز مع تقنية واي فاي (لون فضي مصنفر، 16+ 512 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>5385.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ريدمي باد 2 الجيل الرابع 4G وذاكرة رام 8 جيجابايت وروم 256 جيجابايت، بشاشة 11 بوصة FHD+ 90 هرتز وكاميرا 8MP وبطارية 9000 مللي امبير في الساعة، مكبرات صوت رباعية من شاومي، رمادي (Graphite)</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>1273.36 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>شاشة حماية من الزجاج المقوى لجهاز شاومي باد 5 / باد 5 برو 2021 11 بوصة</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>24.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>محول تيار متردد/مستمر بديل متوافق مع شاحن امدادات الطاقة 5 فولت كورج كاوس باد</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>75.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>محول امدادات الطاقة الرئيسية 12 فولت 2 امبير لكورج كاوس باد KP2</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>75.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محول تيار متردد/تيار مستمر 5 فولت 2 أمبير لبريستيجيو ملتي باد 8.0 PMP5780D PRIME DUO</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>75.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محول تيار متردد اتش ام اند سي ال 5 فولت 2 امبير لتابلت بريستيجيو ملتي باد PMP588ODDuo اندرويد</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>75.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محول تيار متردد 5 فولت 2 أمبير لجهاز تابلت بريستيجيو ملتي باد فيسكونتي PMP810E</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>75.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محول تيار متردد اتش ام اند سي ال 5 فولت 2 أمبير لتابلت بريستيجيو ملتي باد PMP5880D_Duo اندرويد</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>75.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا | 16.7 Million Colors Frameless VESA Compatible, 99% DCI-P3, 120% sRGB,HDMI &amp; DP, Monitor for Work &amp; Gaming</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>519.19 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>422.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل لوحدة المعالجة المركزية 240 كور 2 من كولر ماستر، R9|U7|i7 بمضخة G9R مزدوجة ومرآة انفينيتي aRGB وأنبوب 40 سم ورادياتور 240 ملم ومروحة BWM 12 سم AMD رايزن AM5|4 انتل LGA 1851|1700</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>297.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>447.27 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>1686.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>492.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب منحنية مقاس 27 انش 280 هرتز FHD (1920x1080P) من ايسنو | شاشة عرض 240 هرتز 1 مللي ثانية (جي تي جي) فري سينك 1800R 100%sRGB DP HDMI فيسا مناسبة للمكاتب والألعاب الرياضية الإلكترونية</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>477.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>شاشة الألعاب الاحترافية UG25I بحجم 24.5 بوصة - 240Hz/1ms/فري سينك بريميوم - دقة وضوح FHD (1920x1080) - تصميم بدون إطار - تدعم DP و HDMI من زد ايدج</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>429.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>279.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>ديل شاشة العاب 24 - SE2426HG، FHD (1920×1080)، 240Hz، تقنية IPS سريعة، 0.5 مللي ثانية، AMD فري سينك بريميوم، 99% sRGB، HDR10، فيسا (100×100 ملم)، منفذ عرض، 2 HDMI، ضمان 3 سنوات، اسود</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب منحنية فائقة الاتساع 34 بوصة 240 هرتز فري سينك، 1500R، WQHD 3440×1440، 100% sRGB، 1.07 لون، 350 شمعة/م²، 21:9، VA، 1ms 4000:1، ارتفاع قابل للتعديل، 2X DP و2X HDMI AG34P من زد-ايدج | 1ms/Height Adjustable/1500R/100% sRGB/1.07 Colors/350 cd/㎡/2X DP and 2X HDMI/for Gaming</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>1099.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>559.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>370.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 32 بوصة FHD 240 هرتز، منحنية 1800R 1080 بكسل (1920 × 1080) فري سينك 100% فضاء لوني ار جي بي، 1 مللي ثانية (GTG) فيسا مناسبة للألعاب الرياضية الإلكترونية والمكتب المنزلي من جاوفولك | FHD(1920x1080) Computer Monitors Fast 1ms(GTG) Freesync 100%sRGB VESA Suitable for e-sports games, office, and home use</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>592.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>38.39 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة | 3 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من إينيو بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج S23 وS22 وآيباد، منفذين، 30 واط، شحن سريع وتصميم مدمج | All-Metal, Intelligent Safety Protection, Mini Type-C Car Charger for iPhone 17 16 Pro Max Samsung S26 S25 Huawei Honor etc</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>35.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج | fast charge for MacBook&amp;laptops, Charge 3 devices simultaneously,Intelligent safety protection,for long road trips</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>35.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Ideal for daily commute,Smart safety protection</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>39.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب | Cigarette Lighter with 65W Retractable Cable, USB C and USB A Charging Ports, Voltage Display, for iPhone/Android/iPad/Laptop</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 2 devices simultaneously,for daily commute</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>68.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>شاحن جوال للسيارة قابل للسحب فائق السرعة بقدرة 120 واط، متوافق مع جوالات ابل ايفون واندرويد</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>37.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>59.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-28</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>56.14 ر.س</t>
+          <t>38.95 ر.س</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -679,35 +679,35 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,70 +749,70 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>553.78 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>20.78 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>60.98 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>64.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1819,17 +1819,17 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1973,17 +1973,17 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -1995,44 +1995,44 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>94.97 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>118.99 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>171.0 ر.س</t>
+          <t>17.72 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع | منفاخ إطارات مع شاشة رقمية مزدوجة القيم، مضخة إطارات السيارات مع مصابيح LED للسيارات والدراجات النارية والدراجات والكرات</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>99.98 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>باور بانك زولو 20,000 مللي أمبير في الساعة و30 واط، شاحن محمول فائق السرعة مع كيبل USB-C مدمج، حزمة بطارية متوافقة مع سلسلة آيفون 17/17 إير/17 برو/17 برو ماكس/16 وجالكسي والمزيد من أنكر، أزرق</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>11.17 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب-A مع شحن سريع وحماية للابتوب والهاتف الذكي 3 منافذ | high-capacity, flight-safe, ultra-fast 100W charging(2C1A), 65W self-charging, for MacBook/Samsung/iPhone/iPad</t>
+          <t>مضخة مياه، موزع مياه قابل لإعادة الشحن مع شاحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 ل للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر من لوازم، 12.8 سم × 69 ملم</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>178.86 ر.س</t>
+          <t>12.6 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم بوليمر بمنفذ USB-C مع كابل مدمج وشحن سريع للهاتف الذكي واللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, high capacity, charges 3 devices at once, for Tablets/Phone</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>17.72 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج | شاحن عالي السعة وآمن للاستخدام أثناء الطيران، يدعم الشحن السريع لثلاثة أجهزة، وشاشة عرض رقمية لأجهزة MacBook Air iPad</t>
+          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>178.94 ر.س</t>
+          <t>21.97 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>139.99 ر.س</t>
+          <t>11.25 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000 | حزمة بطارية 20,000 مللي أمبير في الساعة مع كابلات مدمجة مزدوجة، منافذ USB-C وUSB-A لسلسلة ايفون 17 / 16 وجالكسي وماك بوك</t>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>178.8 ر.س</t>
+          <t>106.3 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها | Detachable USB C Cable, Flight-Safe, Travel Essential, External Phone Battery Pack for iPhone 17 Samsung S26 Honor iPad etc</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>111.14 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ | Flight-Approved, smart digital display, 130W ultra-fast charging, charge 3 devices at once, for Laptop/MacBook/iPhone/Samsung</t>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>198.83 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>26.0 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>شاومي باور بانك 67 واط 20,000 مللي امبير في الساعة مع كابل مدمج - شاحن سريع محمول بيج داكن</t>
+          <t>استرو ايه اي ضاغط هواء محمول لنفخ الاطارات 12 فولت تيار مستمر 150 باوند لكل | مضخة كهربائية لإطارات السيارة مع مقياس ضغط الإطارات، منفاخ إطارات بخاصية الإيقاف التلقائي مع محولات صمام ومصباح LED، لون أصفر</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>119.98 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن جيجابت PoE 802.3at/af | محول غير PoE الى PoE | لوازم PoE (15.4 واط) او PoE+ (30 واط) | التوصيل والتشغيل | سطح المكتب/الحائط | مسافة تصل الى 100 متر (PoE160S)</t>
+          <t>مضخة موزع مياه من لوازم بتصميم حديث، براد ماء بشكل مستدير، مصنوع من ستانلس ستيل وبلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>85.0 ر.س</t>
+          <t>15.84 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>46.0 ر.س</t>
+          <t>88.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>46.0 ر.س</t>
+          <t>135.15 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>295.0 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة | منفذ 1G، PoE+ أو تيار مستمر، محول متضمن، ضمان 5 سنوات، بوابة كابتيف، شبكة، تجوال WPA3، تجربة واي فاي للأعمال</t>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>327.26 ر.س</t>
+          <t>78.7 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن TL-POE170S PoE++ (منفذين جيجابت، متوافق مع 802.3af /at/bt، إجمالي الطاقة بقدرة تصل إلى 60 واط، تصميم يثبت على الحائط وسطح المكتب، التوصيل والتشغيل) اسود</t>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود | 3-Output Fast Charging, Flight-Safe for Travel, Phone Holder, Mini Battery Pack for iPhone 17 16 Samsung S25 S24 Honor etc</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>183.0 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك راوتر خارجي MR402 خارجي 4G LTE من ارتشر، واي فاي AC1200Mbps ثنائي النطاق، مقاوم للماء IP65، دعم POE/DC، كات 4 حتى 150 ميجابت في الثانية، تقنية ون ميش، تركيب عمود/حائط، توصيل وتشغيل</t>
+          <t>باور بانك، شاحن محمول صغير 22.5 واط USB C 10000mAh، حزمة بطارية شحن سريع PD 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>289.0 ر.س</t>
+          <t>74.9 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>221.61 ر.س</t>
+          <t>118.99 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>48.49 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت | Ultra-Slim, skin-friendly, ergonomic design, flight-safe, PD 15W Wired Charging, Qi 7.5W Magnetic for iPhone 17/16/15/14/13</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك WLAN Access P. 300mb في الهواء الطلق, CPE210 | وصلة لاسلكية طويلة المدى. هوائي اتجاهي عالي الكسب. مثالية للاستخدام في الهواء الطلق. نقل من نقطة إلى نقطة.</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>220.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,1335 +2638,15 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>298.79 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>مضخة هواء كهربائية مع 3 فوهات من سكاي تاتش مضخة نفخ مزدوجة الاستخدام للسيارة العائلية سريعة الملء مثالية للأسرة الهوائية والتخييم في الهواء الطلق والقوارب وعوامات السباحة ولعبة الطوافة (أسود)</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>23.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>17.72 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>11.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>21.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>11.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه، موزع مياه قابل لإعادة الشحن مع شاحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 ل للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر من لوازم، 12.8 سم × 69 ملم</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>12.6 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>17.72 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>106.55 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>منفاخ هواء من إنتكس أوتوماتيكي مع 3 فوهات قابلة للتوصيل كهربائي سلكي</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>77.23 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>26.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>15.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>مضخة موزع مياه من لوازم بتصميم حديث، براد ماء بشكل مستدير، مصنوع من ستانلس ستيل وبلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>15.84 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>استرو ايه اي ضاغط هواء محمول لنفخ الاطارات 12 فولت تيار مستمر 150 باوند لكل | مضخة كهربائية لإطارات السيارة مع مقياس ضغط الإطارات، منفاخ إطارات بخاصية الإيقاف التلقائي مع محولات صمام ومصباح LED، لون أصفر</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>119.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>منفاخ هواء يدوي مريح محمول بمقبض من الفولاذ على شكل حرف T وخرطوم نفخ وصمام متوافق وألوان مختلطة لإطارات الدراجات والكرات ومعدات التخييم</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>12.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>1779.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في | دقة 2.8 كيه، ضوء 509 غرام، شحن فائق 66 واط، قلم ام الجيل الثالث + كيبورد مغناطيسي + ماوس + عبوة عناية الكل في واحد</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>3499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 مي، 6GB + 128GB، رمادي، شاشة 11 انش 2.5K 90Hz بطارية 9000mAh، ام تي كيه هيليو G100-Ultra 8MP مع مكبرات صوت رباعية</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>984.04 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>اونر تابلت باد 9 12.1 انش 8GB/256GB 2 5K 12.1 انش 2.5K 120Hz 8300mAh واي فاي 5 بلاتا</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>1868.82 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB | دقة 2.8K، وزن 509 جم، شحن فائق السرعة 66 واط، قلم M-بنسل من الجيل الثالث + لوحة مفاتيح مغناطيسية + ماوس + باقة كير متكاملة</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>3599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ون بلس باد 3 سناب دراجون® 8 ايليت معدل تحديث 144 هرتز مع تقنية واي فاي (لون فضي مصنفر، 16+ 512 جيجابايت)</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>5385.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ريدمي باد 2 الجيل الرابع 4G وذاكرة رام 8 جيجابايت وروم 256 جيجابايت، بشاشة 11 بوصة FHD+ 90 هرتز وكاميرا 8MP وبطارية 9000 مللي امبير في الساعة، مكبرات صوت رباعية من شاومي، رمادي (Graphite)</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>1273.36 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>شاشة حماية من الزجاج المقوى لجهاز شاومي باد 5 / باد 5 برو 2021 11 بوصة</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>24.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>محول تيار متردد/مستمر بديل متوافق مع شاحن امدادات الطاقة 5 فولت كورج كاوس باد</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>75.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>محول امدادات الطاقة الرئيسية 12 فولت 2 امبير لكورج كاوس باد KP2</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>75.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محول تيار متردد/تيار مستمر 5 فولت 2 أمبير لبريستيجيو ملتي باد 8.0 PMP5780D PRIME DUO</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>75.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محول تيار متردد اتش ام اند سي ال 5 فولت 2 امبير لتابلت بريستيجيو ملتي باد PMP588ODDuo اندرويد</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>75.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محول تيار متردد 5 فولت 2 أمبير لجهاز تابلت بريستيجيو ملتي باد فيسكونتي PMP810E</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>75.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محول تيار متردد اتش ام اند سي ال 5 فولت 2 أمبير لتابلت بريستيجيو ملتي باد PMP5880D_Duo اندرويد</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>75.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا | 16.7 Million Colors Frameless VESA Compatible, 99% DCI-P3, 120% sRGB,HDMI &amp; DP, Monitor for Work &amp; Gaming</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>519.19 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>422.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل لوحدة المعالجة المركزية 240 كور 2 من كولر ماستر، R9|U7|i7 بمضخة G9R مزدوجة ومرآة انفينيتي aRGB وأنبوب 40 سم ورادياتور 240 ملم ومروحة BWM 12 سم AMD رايزن AM5|4 انتل LGA 1851|1700</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>297.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>447.27 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>1686.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>492.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب منحنية مقاس 27 انش 280 هرتز FHD (1920x1080P) من ايسنو | شاشة عرض 240 هرتز 1 مللي ثانية (جي تي جي) فري سينك 1800R 100%sRGB DP HDMI فيسا مناسبة للمكاتب والألعاب الرياضية الإلكترونية</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>477.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>شاشة الألعاب الاحترافية UG25I بحجم 24.5 بوصة - 240Hz/1ms/فري سينك بريميوم - دقة وضوح FHD (1920x1080) - تصميم بدون إطار - تدعم DP و HDMI من زد ايدج</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>429.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>279.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>ديل شاشة العاب 24 - SE2426HG، FHD (1920×1080)، 240Hz، تقنية IPS سريعة، 0.5 مللي ثانية، AMD فري سينك بريميوم، 99% sRGB، HDR10، فيسا (100×100 ملم)، منفذ عرض، 2 HDMI، ضمان 3 سنوات، اسود</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب منحنية فائقة الاتساع 34 بوصة 240 هرتز فري سينك، 1500R، WQHD 3440×1440، 100% sRGB، 1.07 لون، 350 شمعة/م²، 21:9، VA، 1ms 4000:1، ارتفاع قابل للتعديل، 2X DP و2X HDMI AG34P من زد-ايدج | 1ms/Height Adjustable/1500R/100% sRGB/1.07 Colors/350 cd/㎡/2X DP and 2X HDMI/for Gaming</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>1099.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>559.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>370.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 32 بوصة FHD 240 هرتز، منحنية 1800R 1080 بكسل (1920 × 1080) فري سينك 100% فضاء لوني ار جي بي، 1 مللي ثانية (GTG) فيسا مناسبة للألعاب الرياضية الإلكترونية والمكتب المنزلي من جاوفولك | FHD(1920x1080) Computer Monitors Fast 1ms(GTG) Freesync 100%sRGB VESA Suitable for e-sports games, office, and home use</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>592.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>38.39 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة | 3 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من إينيو بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج S23 وS22 وآيباد، منفذين، 30 واط، شحن سريع وتصميم مدمج | All-Metal, Intelligent Safety Protection, Mini Type-C Car Charger for iPhone 17 16 Pro Max Samsung S26 S25 Huawei Honor etc</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>35.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج | fast charge for MacBook&amp;laptops, Charge 3 devices simultaneously,Intelligent safety protection,for long road trips</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>20.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>35.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>75.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Ideal for daily commute,Smart safety protection</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>39.18 ر.س</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب | Cigarette Lighter with 65W Retractable Cable, USB C and USB A Charging Ports, Voltage Display, for iPhone/Android/iPad/Laptop</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 2 devices simultaneously,for daily commute</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>68.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>شاحن جوال للسيارة قابل للسحب فائق السرعة بقدرة 120 واط، متوافق مع جوالات ابل ايفون واندرويد</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>37.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>59.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-29</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>38.95 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم</t>
+          <t>منصة JODA هوم فولت 4 بطاريات وايرليس بسعة 10000 ملي امبير منفذ تايب سي مع كيبل مدمج تايب سي</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>459.0 ر.س</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>شاحن JODA MagiX اربعة في واحد لساعة ابل + ايربودز + ايفون + منفذ تايب سي - اسود</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>299.0 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
+          <t>شاحن JODA MagiX اربعة في واحد لساعة ابل + ايربودز + ايفون + منفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>299.0 ر.س</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول مترين - اسود</t>
+          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>19.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول مترين - اسود</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>19.0 ر.س</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 20 واط بمنفذ تايب سي - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>شاحن سيارة JODA بقوة 20 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هوم فولت 4 بطاريات وايرليس بسعة 10000 ملي امبير منفذ تايب سي مع كيبل مدمج تايب سي</t>
+          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>459.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2033,622 +2033,6 @@
       <c r="D56" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>17.72 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع | منفاخ إطارات مع شاشة رقمية مزدوجة القيم، مضخة إطارات السيارات مع مصابيح LED للسيارات والدراجات النارية والدراجات والكرات</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>99.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>11.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه، موزع مياه قابل لإعادة الشحن مع شاحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 ل للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر من لوازم، 12.8 سم × 69 ملم</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>12.6 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>17.72 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>21.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>11.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>106.3 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>15.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>15.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>26.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>استرو ايه اي ضاغط هواء محمول لنفخ الاطارات 12 فولت تيار مستمر 150 باوند لكل | مضخة كهربائية لإطارات السيارة مع مقياس ضغط الإطارات، منفاخ إطارات بخاصية الإيقاف التلقائي مع محولات صمام ومصباح LED، لون أصفر</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>119.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>مضخة موزع مياه من لوازم بتصميم حديث، براد ماء بشكل مستدير، مصنوع من ستانلس ستيل وبلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>15.84 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>135.15 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>295.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>78.7 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود | 3-Output Fast Charging, Flight-Safe for Travel, Phone Holder, Mini Battery Pack for iPhone 17 16 Samsung S25 S24 Honor etc</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك، شاحن محمول صغير 22.5 واط USB C 10000mAh، حزمة بطارية شحن سريع PD 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>74.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>94.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>118.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت | Ultra-Slim, skin-friendly, ergonomic design, flight-safe, PD 15W Wired Charging, Qi 7.5W Magnetic for iPhone 17/16/15/14/13</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>298.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-30</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أسود</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - تيتانيوم</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أسود</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1819,17 +1819,17 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -1973,64 +1973,20 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>wjhtektelecome</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>149.01 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>alwan7</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>50.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-08-31</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-01</t>
         </is>
       </c>
     </row>
@@ -644,35 +644,35 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>297.8 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>297.8 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,35 +749,35 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>533.1 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>سلك JODA سيليكون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اخصر</t>
+          <t>ضمان : 24 شهر</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>34.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول مترين - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول مترين - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>19.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
+          <t>شاحن سيارة JODA بقوة 20 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
+          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1203,17 +1203,17 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 20 واط بمنفذ تايب سي - اسود</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1225,17 +1225,17 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أسود</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1731,61 +1731,61 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1929,17 +1929,17 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1951,44 +1951,330 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
+          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>599.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>مبرد سائل لوحدة المعالجة المركزية 240 كور 2 من كولر ماستر، R9|U7|i7 بمضخة G9R مزدوجة ومرآة انفينيتي aRGB وأنبوب 40 سم ورادياتور 240 ملم ومروحة BWM 12 سم AMD رايزن AM5|4 انتل LGA 1851|1700</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>297.8 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا | 16.7 Million Colors Frameless VESA Compatible, 99% DCI-P3, 120% sRGB,HDMI &amp; DP, Monitor for Work &amp; Gaming</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>549.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>459.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>539.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>279.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>617.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب سامسونج 27 انش، QHD (2560 × 1440)، معدل تحديث 240Hz، وقت استجابة 1 مللي ثانية، ذكي، اسود، كوانتوم دوت، HDR600، LS27BG650EMXUE</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>1272.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>498.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>شاشة الألعاب الاحترافية UG25I بحجم 24.5 بوصة - 240Hz/1ms/فري سينك بريميوم - دقة وضوح FHD (1920x1080) - تصميم بدون إطار - تدعم DP و HDMI من زد ايدج</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>465.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>370.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 24.5 انش 300 هرتز 280 هرتز 240 هرتز UG25S FHD 1080p فائقة السرعة ام بي ار تي 1ms شاشة IPS للألعاب، شاشة كمبيوتر 16.7 مليون لون، DP x2، HDMI x2 من زد-ايدج</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>619.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>شاشة تي يو اف للألعاب طراز VG27AQM5A مقاس 27 بوصة بدقة FHD (1920×1080) وتردد 240 هرتز، لوحة IPS فاست بزمن استجابة 0.3 ميلي ثانية مع تقنيات جي سينك وفري سينك وألوان ار جي بي وديسبلاي ويدجيت من اسوس</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>795.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>479.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>شاشة عرض للالعاب VX3219-PC-MHD منحنية قياس 32 انش بعرض HD 1080P،240Hz و1ms، تتضمن مكبرات صوت مزدوجة مدمجة بتزامن تكيفي و2 × HDMI ومنفذ عرض من فيوسونيك، بلون اسود، LED</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>597.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-01</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -644,35 +644,35 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>297.8 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>297.8 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,70 +749,70 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>aletawiksa, amazon_sa</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>533.1 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>64.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>58.92 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
+          <t>خلطة فيز 160 جم من هاريبو</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>599.0 ر.س</t>
+          <t>11.95 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>مبرد سائل لوحدة المعالجة المركزية 240 كور 2 من كولر ماستر، R9|U7|i7 بمضخة G9R مزدوجة ومرآة انفينيتي aRGB وأنبوب 40 سم ورادياتور 240 ملم ومروحة BWM 12 سم AMD رايزن AM5|4 انتل LGA 1851|1700</t>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>297.8 ر.س</t>
+          <t>8.99 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا | 16.7 Million Colors Frameless VESA Compatible, 99% DCI-P3, 120% sRGB,HDMI &amp; DP, Monitor for Work &amp; Gaming</t>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>549.99 ر.س</t>
+          <t>17.95 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>459.99 ر.س</t>
+          <t>11.95 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>539.0 ر.س</t>
+          <t>7.95 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>279.99 ر.س</t>
+          <t>11.95 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>617.0 ر.س</t>
+          <t>5.99 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب سامسونج 27 انش، QHD (2560 × 1440)، معدل تحديث 240Hz، وقت استجابة 1 مللي ثانية، ذكي، اسود، كوانتوم دوت، HDR600، LS27BG650EMXUE</t>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>1272.0 ر.س</t>
+          <t>16.95 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>498.78 ر.س</t>
+          <t>15.5 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>شاشة الألعاب الاحترافية UG25I بحجم 24.5 بوصة - 240Hz/1ms/فري سينك بريميوم - دقة وضوح FHD (1920x1080) - تصميم بدون إطار - تدعم DP و HDMI من زد ايدج</t>
+          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>465.49 ر.س</t>
+          <t>12.5 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>370.0 ر.س</t>
+          <t>15.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب 24.5 انش 300 هرتز 280 هرتز 240 هرتز UG25S FHD 1080p فائقة السرعة ام بي ار تي 1ms شاشة IPS للألعاب، شاشة كمبيوتر 16.7 مليون لون، DP x2، HDMI x2 من زد-ايدج</t>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>619.99 ر.س</t>
+          <t>12.5 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>شاشة تي يو اف للألعاب طراز VG27AQM5A مقاس 27 بوصة بدقة FHD (1920×1080) وتردد 240 هرتز، لوحة IPS فاست بزمن استجابة 0.3 ميلي ثانية مع تقنيات جي سينك وفري سينك وألوان ار جي بي وديسبلاي ويدجيت من اسوس</t>
+          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>795.15 ر.س</t>
+          <t>12.5 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+          <t>حلوى هابي كولا من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>479.0 ر.س</t>
+          <t>16.75 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,15 +2264,675 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>شاشة عرض للالعاب VX3219-PC-MHD منحنية قياس 32 انش بعرض HD 1080P،240Hz و1ms، تتضمن مكبرات صوت مزدوجة مدمجة بتزامن تكيفي و2 × HDMI ومنفذ عرض من فيوسونيك، بلون اسود، LED</t>
+          <t>حلوى مضغ ميكس فوارة من هاريبو، 70 جرام</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>597.5 ر.س</t>
+          <t>7.25 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن جيجابت PoE 802.3at/af | محول غير PoE الى PoE | لوازم PoE (15.4 واط) او PoE+ (30 واط) | التوصيل والتشغيل | سطح المكتب/الحائط | مسافة تصل الى 100 متر (PoE160S)</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن TL-POE170S PoE++ (منفذين جيجابت، متوافق مع 802.3af /at/bt، إجمالي الطاقة بقدرة تصل إلى 60 واط، تصميم يثبت على الحائط وسطح المكتب، التوصيل والتشغيل) اسود</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>183.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>48.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة | منفذ 1G، PoE+ أو تيار مستمر، محول متضمن، ضمان 5 سنوات، بوابة كابتيف، شبكة، تجوال WPA3، تجربة واي فاي للأعمال</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>352.68 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك مجموعة جسر EAP211، جسر لاسلكي من نقطة الى نقطة، 3 منافذ جيجابت، للاستخدام الخارجي والداخلي، نطاق طويل 1 كم، PtP &amp; PtMP، مدى طويل 1 كم، يعمل عبر الايثرنت او تيار مستمر، ادارة مركزية، تكوين</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>489.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>221.63 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210 | C310 C320WS TC60 TC70 C211 C110، كاميرا مراقبة داخلية، كابل محول طاقة بديل</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>97.6 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>136.56 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>38.39 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة | 3 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج | fast charge for MacBook&amp;laptops, Charge 3 devices simultaneously,Intelligent safety protection,for long road trips</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من إينيو بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج S23 وS22 وآيباد، منفذين، 30 واط، شحن سريع وتصميم مدمج | All-Metal, Intelligent Safety Protection, Mini Type-C Car Charger for iPhone 17 16 Pro Max Samsung S26 S25 Huawei Honor etc</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>35.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>35.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Ideal for daily commute,Smart safety protection</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>39.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>شاحن جوال للسيارة قابل للسحب فائق السرعة بقدرة 120 واط، متوافق مع جوالات ابل ايفون واندرويد</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>37.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>59.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 2 devices simultaneously,for daily commute</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>68.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب | Cigarette Lighter with 65W Retractable Cable, USB C and USB A Charging Ports, Voltage Display, for iPhone/Android/iPad/Laptop</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-02</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>aletawiksa, al3bor-telecom</t>
+          <t>aletawiksa, al3bor-telecom, amazon_sa</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>40.19 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>181.38 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -784,35 +784,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>58.92 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>64.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,17 +1775,17 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1929,17 +1929,17 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1951,44 +1951,44 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>11.95 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>11.95 ر.س</t>
+          <t>5.99 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>7.95 ر.س</t>
+          <t>40.19 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>11.95 ر.س</t>
+          <t>328.33 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>5.99 ر.س</t>
+          <t>285.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>16.95 ر.س</t>
+          <t>98.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>15.5 ر.س</t>
+          <t>217.0 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>12.5 ر.س</t>
+          <t>197.71 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>15.0 ر.س</t>
+          <t>110.61 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>12.5 ر.س</t>
+          <t>205.16 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
+          <t>فستان كاجوال للنساء من هاربا، عبوة من قطعة واحدة، GR6356</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>12.5 ر.س</t>
+          <t>65.14 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 200 جم</t>
+          <t>ساعة منبه ران اواي المتدحرجة (الأصلية) من كلوكي، بصوت عال جدا الثقيل (روبوت غرفة النوم للكبار والأطفال) مضحكة، متدحرجة، هاربة، متحركة، قافزة (أزرق)</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>16.75 ر.س</t>
+          <t>168.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>حلوى مضغ ميكس فوارة من هاريبو، 70 جرام</t>
+          <t>وايلد ريبابليك نسر هاربي من رينفوريست، حيوان محشو، 4.5 انش، لعبة محشوة، زجاجات مياه معاد تدويرها، صديقة للبيئة</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>7.25 ر.س</t>
+          <t>52.88 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن جيجابت PoE 802.3at/af | محول غير PoE الى PoE | لوازم PoE (15.4 واط) او PoE+ (30 واط) | التوصيل والتشغيل | سطح المكتب/الحائط | مسافة تصل الى 100 متر (PoE160S)</t>
+          <t>خيوط غزل بلون هاربي من ليون براند يارن، 3 عبوات، 525-227-3</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>85.0 ر.س</t>
+          <t>331.26 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,631 +2308,15 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>هارمونيكا هارب هارموك ارمونيكا 24 فتحة فم، مفتاح احترافي سي متعدد الأصوات دياتونيك مع حافظة لموسيقى البوب والجاز الشعبي البلوز</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>166.85 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>66.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>40.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>66.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن TL-POE170S PoE++ (منفذين جيجابت، متوافق مع 802.3af /at/bt، إجمالي الطاقة بقدرة تصل إلى 60 واط، تصميم يثبت على الحائط وسطح المكتب، التوصيل والتشغيل) اسود</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>183.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>66.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>48.49 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة | منفذ 1G، PoE+ أو تيار مستمر، محول متضمن، ضمان 5 سنوات، بوابة كابتيف، شبكة، تجوال WPA3، تجربة واي فاي للأعمال</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>352.68 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك مجموعة جسر EAP211، جسر لاسلكي من نقطة الى نقطة، 3 منافذ جيجابت، للاستخدام الخارجي والداخلي، نطاق طويل 1 كم، PtP &amp; PtMP، مدى طويل 1 كم، يعمل عبر الايثرنت او تيار مستمر، ادارة مركزية، تكوين</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>489.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>221.63 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210 | C310 C320WS TC60 TC70 C211 C110، كاميرا مراقبة داخلية، كابل محول طاقة بديل</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>97.6 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>186.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>136.56 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>38.39 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة | 3 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج | fast charge for MacBook&amp;laptops, Charge 3 devices simultaneously,Intelligent safety protection,for long road trips</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من إينيو بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج S23 وS22 وآيباد، منفذين، 30 واط، شحن سريع وتصميم مدمج | All-Metal, Intelligent Safety Protection, Mini Type-C Car Charger for iPhone 17 16 Pro Max Samsung S26 S25 Huawei Honor etc</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>35.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>35.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Ideal for daily commute,Smart safety protection</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>39.18 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>شاحن جوال للسيارة قابل للسحب فائق السرعة بقدرة 120 واط، متوافق مع جوالات ابل ايفون واندرويد</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>37.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>59.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>45.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 2 devices simultaneously,for daily commute</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>68.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب | Cigarette Lighter with 65W Retractable Cable, USB C and USB A Charging Ports, Voltage Display, for iPhone/Android/iPad/Laptop</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -489,7 +489,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-04</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>11.95 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>17.95 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>118.99 ر.س</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>7.95 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ | Flight-Approved, smart digital display, 130W ultra-fast charging, charge 3 devices at once, for Laptop/MacBook/iPhone/Samsung</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>14.5 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج | شاحن عالي السعة وآمن للاستخدام أثناء الطيران، يدعم الشحن السريع لثلاثة أجهزة، وشاشة عرض رقمية لأجهزة MacBook Air iPad</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>5.99 ر.س</t>
+          <t>178.94 ر.س</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, high capacity, charges 3 devices at once, for Tablets/Phone</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 8 في 1 مع 4 كابلات USB-C مدمجة، 2 منفذ USB-A ونوع C، شاشة LED للطاقة، مصباح يدوي، بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>16.48 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 22.5 واط شحن سريع، اصغر من معظم الشواحن 20 كلفن، باور بانك محمول مع كيبل مدمج، 4 مخارج وشاشة LED، مناسب للسفر لاجهزة ايفون وسامسونج والتابلت (ابيض)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>16.95 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>11.95 ر.س</t>
+          <t>139.99 ر.س</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>9.95 ر.س</t>
+          <t>189.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000 | حزمة بطارية 20,000 مللي أمبير في الساعة مع كابلات مدمجة مزدوجة، منافذ USB-C وUSB-A لسلسلة ايفون 17 / 16 وجالكسي وماك بوك</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>178.8 ر.س</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها | Detachable USB C Cable, Flight-Safe, Travel Essential, External Phone Battery Pack for iPhone 17 Samsung S26 Honor iPad etc</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>15.0 ر.س</t>
+          <t>129.99 ر.س</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من بي دي بيست مع كابل مدمج، شحن سريع USB نوع سي 22.5 واط | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>12.5 ر.س</t>
+          <t>119.99 ر.س</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -2146,15 +2146,345 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>حلوى إسفنجية من هاريبو، 80 جرام</t>
+          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>خلطة فيز 160 جم من هاريبو</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>11.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>14.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>17.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>8.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
           <t>7.95 ر.س</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>11.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>7.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>16.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>16.48 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>15.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>9.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>12.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 200 جم</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>16.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -489,7 +489,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-05</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أسود</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1827,666 +1827,6 @@
       <c r="D47" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>94.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>118.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ | Flight-Approved, smart digital display, 130W ultra-fast charging, charge 3 devices at once, for Laptop/MacBook/iPhone/Samsung</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>198.82 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج | شاحن عالي السعة وآمن للاستخدام أثناء الطيران، يدعم الشحن السريع لثلاثة أجهزة، وشاشة عرض رقمية لأجهزة MacBook Air iPad</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>178.94 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, high capacity, charges 3 devices at once, for Tablets/Phone</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 8 في 1 مع 4 كابلات USB-C مدمجة، 2 منفذ USB-A ونوع C، شاشة LED للطاقة، مصباح يدوي، بطارية عالية السعة للجوال والتابلت</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>99.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 22.5 واط شحن سريع، اصغر من معظم الشواحن 20 كلفن، باور بانك محمول مع كيبل مدمج، 4 مخارج وشاشة LED، مناسب للسفر لاجهزة ايفون وسامسونج والتابلت (ابيض)</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>99.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>139.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>189.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000 | حزمة بطارية 20,000 مللي أمبير في الساعة مع كابلات مدمجة مزدوجة، منافذ USB-C وUSB-A لسلسلة ايفون 17 / 16 وجالكسي وماك بوك</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>178.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها | Detachable USB C Cable, Flight-Safe, Travel Essential, External Phone Battery Pack for iPhone 17 Samsung S26 Honor iPad etc</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>129.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من بي دي بيست مع كابل مدمج، شحن سريع USB نوع سي 22.5 واط | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>119.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>11.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>14.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>17.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>8.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>7.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>11.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>7.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>16.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>12.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>16.48 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>15.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>9.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>12.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>حلوى هابي كولا من هاريبو، 200 جم</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>16.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>12.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -43,7 +43,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +109,9 @@
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-06</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -577,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>al3bor-telecom, amazon_sa</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>40.19 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>216.07 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -671,35 +679,35 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>80.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>80.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -741,35 +749,35 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -787,21 +795,21 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>aletawiksa, amazon_sa</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>57.01 ر.س</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -824,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -863,970 +871,2598 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>ضمان : 24 شهر</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>5.0 ر.س</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>عروض الكفرات</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>عروض الكفرات</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>99.0 ر.س</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>119.0 ر.س</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>159.0 ر.س</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>209.0 ر.س</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>349.0 ر.س</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>49.0 ر.س</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>alwan7</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>50.0 ر.س</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>40.19 ر.س</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>دار الأداب الهاربون والباقون</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>98.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>285.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>303.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>328.33 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>217.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>110.61 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>روبوتايم 3 دي بازل هارب</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>204.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>فستان كاجوال للنساء من هاربا، عبوة من قطعة واحدة، GR6356</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>65.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>ساعة منبه ران اواي المتدحرجة (الأصلية) من كلوكي، بصوت عال جدا الثقيل (روبوت غرفة النوم للكبار والأطفال) مضحكة، متدحرجة، هاربة، متحركة، قافزة (أزرق)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>168.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>283.69 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>291.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>الملاك الهارب</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>52.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>276.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>217.13 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن جيجابت PoE 802.3at/af | محول غير PoE الى PoE | لوازم PoE (15.4 واط) او PoE+ (30 واط) | التوصيل والتشغيل | سطح المكتب/الحائط | مسافة تصل الى 100 متر (PoE160S)</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>289.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن TL-POE170S PoE++ (منفذين جيجابت، متوافق مع 802.3af /at/bt، إجمالي الطاقة بقدرة تصل إلى 60 واط، تصميم يثبت على الحائط وسطح المكتب، التوصيل والتشغيل) اسود</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>183.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>48.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة | منفذ 1G، PoE+ أو تيار مستمر، محول متضمن، ضمان 5 سنوات، بوابة كابتيف، شبكة، تجوال WPA3، تجربة واي فاي للأعمال</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>364.48 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك نقطة وصول لاسلكية تثبت بالسقف بسرعة 300 ميجابت في الثانية EAP115</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>129.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك راوتر خارجي MR402 خارجي 4G LTE من ارتشر، واي فاي AC1200Mbps ثنائي النطاق، مقاوم للماء IP65، دعم POE/DC، كات 4 حتى 150 ميجابت في الثانية، تقنية ون ميش، تركيب عمود/حائط، توصيل وتشغيل</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>289.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>محول مقسم نشط POE من قطعتين، 48 فولت الى 12 فولت، متوافق مع IEEE 802.3af 10/100Mbps حتى 100 متر لكاميرا IP ونقطة الوصول اللاسلكية والهاتف عبر بروتوكول الإنترنت</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210 | C310 C320WS TC60 TC70 C211 C110، كاميرا مراقبة داخلية، كابل محول طاقة بديل</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>97.64 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>80.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>150.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>282.56 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>94.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>118.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 10000 مللي امبير بمنفذ USB تايب-C مع شحن لاسلكي و سريع و مغناطيسي للهاتف الذكي بمنفذين رمادي | Skin-Friendly, Qi certified, 20W wired, ergonomic design, flight-safe, strong magnetic hold, Compatible with iPhone 17/16/15</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>118.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك، شاحن محمول صغير 22.5 واط USB C 10000mAh، حزمة بطارية شحن سريع PD 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت | Ultra-Slim, skin-friendly, ergonomic design, flight-safe, PD 15W Wired Charging, Qi 7.5W Magnetic for iPhone 17/16/15/14/13</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>298.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود | 3-Output Fast Charging, Flight-Safe for Travel, Phone Holder, Mini Battery Pack for iPhone 17 16 Samsung S25 S24 Honor etc</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>1779.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في | دقة 2.8 كيه، ضوء 509 غرام، شحن فائق 66 واط، قلم ام الجيل الثالث + كيبورد مغناطيسي + ماوس + عبوة عناية الكل في واحد</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>اونر تابلت باد في 9 (11.5 انش، واي فاي) 2024 سعة تخزين 256 جيجا، ذاكرة رام 8 جيجا، اندرويد 15 (رمادي)</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>1799.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد 11.5 2025 2.5K 120Hz شاشة ورقية غير لامعة 8+256GB 10100mAh سوبر تشارج 40 واط واي فاي 6 بلوتوث 5.2 WPS اوفيس مكبرات صوت رباعية كيبورد قابلة للفصل، بنفسجي + FOC</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>1731.59 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد 7، ذاكرة RAM 12GB، ذاكرة روم 256GB، 4 هاي بارلانتي، واي فاي، بطارية 8850 mAh، سناب دراجون 7 + الجيل الثالث، اخضر، مع كاريكاب</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>1918.22 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>3499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>ريلمي باد 2 128 جيجا 6 جيجا انسبايراشن جرين واي فاي RMP2205 EU</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>1026.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد 12X 2025 2.8K بشاشة 12 انش غير لامعة 12 انش، 144Hz، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، واي فاي 7، WPS اوفيس و6 مكبرات صوت، كيبورد UItra Light + قلم ام برو مجاني، اخضر</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>2489.31 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3 سناب دراجون® 8 ايليت معدل تحديث 144 هرتز مع تقنية واي فاي (لون فضي مصنفر، 16+ 512 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>5385.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد ميني 12GB+512GB - تابلت 8.8 انش 3K 165Hz، الأبعاد 9400+، 7500mAh 67 واط، 13MP+8MP، هايبر او اس، اسود (مع الشاحن متضمن)</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>2682.22 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>بطارية محمولة L18C4P90 بجهد 15.36 فولت و46 واط في الساعة و2995mAh متوافقة مع لينوفو ثينك باد L13 الجيل الاول SB10T83121 5B10W13933 5B10W13935</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>223.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد ميني 12+512GB ميديا تيك ديمنستي 9400+ شاشة كريستال 3K اصدار واي فاي، شاحن متضمن (اسود)</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>2639.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>تابلت باد 7 من شاومي، 11.2 بوصة، 8+256 جيجا، شاشة 3.2K 144Hz، بطارية سناب دراجون 7+الجيل 3.8850 ميلي أمبير في الساعة، شحن سريع 45 وات، هايبر ايه اي، 4 مكبرات صوت، تجربة سطح المكتب سلسة، مع شاحن، أسود</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>1794.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>تابلت باد 7 11.2 بوصة 8+256 جيجابايت وشاشة 3.2K 144 هرتز، بطارية سناب دراجون 7 +جيل 3 8850 ميلي امبير في الساعة، شحن سريع 45 واط، هايبر ايه اي، 4 مكبرات صوت، تجربة سطح مكتب سلسة وشاحن من شاومي، أخضر</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>1667.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة من سبان لابليد انسترومينتس سوبر بادي 21 سوبر بادي 29، الجزء رقم: 742-00014، SM-72330-3P 7.2 فولت</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>218.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>38.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة | 3 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج | fast charge for MacBook&amp;laptops, Charge 3 devices simultaneously,Intelligent safety protection,for long road trips</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج | All-Metal, Intelligent Safety Protection, Mini Type-C Car Charger for iPhone 17 16 Pro Max Samsung S26 S25 Huawei Honor etc</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>35.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>88.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Ideal for daily commute,Smart safety protection</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>39.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>59.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>35.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب | Cigarette Lighter with 65W Retractable Cable, USB C and USB A Charging Ports, Voltage Display, for iPhone/Android/iPad/Laptop</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 2 devices simultaneously,for daily commute</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>68.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة بقدرة 48 واط مع شحن سريع نوع C ومنفذ USB 3.0 للشحن السريع من موج ماكس، لون أسود</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -43,7 +43,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +109,9 @@
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-08</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -776,35 +784,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>9.96 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>39.48 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>54.55 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -824,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -863,1058 +871,1982 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>ضمان : 24 شهر</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>5.0 ر.س</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>عروض الكفرات</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>عروض الكفرات</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>99.0 ر.س</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>119.0 ر.س</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>9.96 ر.س</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>159.0 ر.س</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>209.0 ر.س</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>349.0 ر.س</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>49.0 ر.س</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>iblackstores</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>171.35 ر.س</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>iblackstores</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>171.35 ر.س</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>iblackstores</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>171.35 ر.س</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>171.35 ر.س</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>149.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>171.35 ر.س</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>149.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>171.35 ر.س</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>149.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>wjhtektelecome</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>149.01 ر.س</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>alwan7</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>50.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>wjhtektelecome</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>149.01 ر.س</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>wjhtektelecome</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>149.01 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن جيجابت PoE 802.3at/af | محول غير PoE الى PoE | لوازم PoE (15.4 واط) او PoE+ (30 واط) | التوصيل والتشغيل | سطح المكتب/الحائط | مسافة تصل الى 100 متر (PoE160S)</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>alwan7</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>50.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>289.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة | منفذ 1G، PoE+ أو تيار مستمر، محول متضمن، ضمان 5 سنوات، بوابة كابتيف، شبكة، تجوال WPA3، تجربة واي فاي للأعمال</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>364.48 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن TL-POE170S PoE++ (منفذين جيجابت، متوافق مع 802.3af /at/bt، إجمالي الطاقة بقدرة تصل إلى 60 واط، تصميم يثبت على الحائط وسطح المكتب، التوصيل والتشغيل) اسود</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>183.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>محول مقسم نشط POE من قطعتين، 48 فولت الى 12 فولت، متوافق مع IEEE 802.3af 10/100Mbps حتى 100 متر لكاميرا IP ونقطة الوصول اللاسلكية والهاتف عبر بروتوكول الإنترنت</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>45.4 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>48.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك WLAN Access P. 300mb في الهواء الطلق, CPE210 | وصلة لاسلكية طويلة المدى. هوائي اتجاهي عالي الكسب. مثالية للاستخدام في الهواء الطلق. نقل من نقطة إلى نقطة.</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>220.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210 | C310 C320WS TC60 TC70 C211 C110، كاميرا مراقبة داخلية، كابل محول طاقة بديل</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>97.51 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك نقطة وصول لاسلكية تثبت بالسقف بسرعة 300 ميجابت في الثانية EAP115</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>129.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في | دقة 2.8 كيه، ضوء 509 غرام، شحن فائق 66 واط، قلم ام الجيل الثالث + كيبورد مغناطيسي + ماوس + عبوة عناية الكل في واحد</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>اونر تابلت باد في 9 (11.5 انش، واي فاي) 2024 سعة تخزين 256 جيجا، ذاكرة رام 8 جيجا، اندرويد 15 (رمادي)</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>1799.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>1348.41 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اس اي 11 انش 4+128 جيجا رمادي، شاشة فل فيو وبطارية كبيرة السعة (مجددة)</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد 7، 11.2 انش، 8+128 جيجا، رمادي، بطارية 8850mAh، شحن تيربو 45 واط، هايبر ايه اي (الشاحن غير متضمن)</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>1029.63 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>1289.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>3499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>بطارية محمولة L18C4P90 بجهد 15.36 فولت و46 واط في الساعة و2995mAh متوافقة مع لينوفو ثينك باد L13 الجيل الاول SB10T83121 5B10W13933 5B10W13935</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>223.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>ريلمي باد 2 128 جيجا 6 جيجا انسبايراشن جرين واي فاي RMP2205 EU</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>1026.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت ريدمي باد 2 مي، 4GB + 128GB، ازرق سيان، ميديا تيك هيليو G100-الترا، شاشة 11 انش 2.5K 90Hz، بطارية 9000mAh، مع شاحن</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>910.57 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>تشو وي تابلت هاي 10 ماكس 33 سم 2880 × 1920 IPS، معالج انتل N150 (4C/4T، حتى 3.6Ghz)، 12GB DDR5، 512GB SSD، ويندوز 11 باد 3 في 1، واي فاي 6، كيبورد عربي</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>2147.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3 سناب دراجون® 8 ايليت معدل تحديث 144 هرتز مع تقنية واي فاي (لون فضي مصنفر، 16+ 512 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>5385.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد ميني 12GB+512GB - تابلت 8.8 انش 3K 165Hz، الأبعاد 9400+، 7500mAh 67 واط، 13MP+8MP، هايبر او اس، اسود (مع الشاحن متضمن)</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>2682.22 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>تابلت باد 7 11.2 بوصة 8+256 جيجابايت وشاشة 3.2K 144 هرتز، بطارية سناب دراجون 7 +جيل 3 8850 ميلي امبير في الساعة، شحن سريع 45 واط، هايبر ايه اي، 4 مكبرات صوت، تجربة سطح مكتب سلسة وشاحن من شاومي، أخضر</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>1667.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>واقي شاشة من جينكيم لأجهزة شاومي إم آي باد 6/6 برو مصنوع من فيلم بملمس ورقي عدد 2 قطعة بملمس الكتابة على الورق</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>39.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>38.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة | 3 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>88.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج | fast charge for MacBook&amp;laptops, Charge 3 devices simultaneously,Intelligent safety protection,for long road trips</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج | All-Metal, Intelligent Safety Protection, Mini Type-C Car Charger for iPhone 17 16 Pro Max Samsung S26 S25 Huawei Honor etc</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>35.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>35.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Ideal for daily commute,Smart safety protection</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>49.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة بقدرة 48 واط مع شحن سريع نوع C ومنفذ USB 3.0 للشحن السريع من موج ماكس، لون أسود</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب | Cigarette Lighter with 65W Retractable Cable, USB C and USB A Charging Ports, Voltage Display, for iPhone/Android/iPad/Laptop</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>شاحن جوال للسيارة قابل للسحب فائق السرعة بقدرة 120 واط، متوافق مع جوالات ابل ايفون واندرويد</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>37.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -43,7 +43,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -63,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,9 +104,6 @@
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,7 +489,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-09</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -784,35 +776,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>9.96 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>54.55 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>39.48 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -871,1982 +863,992 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ضمان : 24 شهر</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>5.0 ر.س</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>عروض الكفرات</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>اكسسوارات ايفون 18</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>عروض الكفرات</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>اكسسوارات ايفون 18</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>99.0 ر.س</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>119.0 ر.س</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>9.96 ر.س</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>159.0 ر.س</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>209.0 ر.س</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>349.0 ر.س</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>49.0 ر.س</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>alwan7</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>50.0 ر.س</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن جيجابت PoE 802.3at/af | محول غير PoE الى PoE | لوازم PoE (15.4 واط) او PoE+ (30 واط) | التوصيل والتشغيل | سطح المكتب/الحائط | مسافة تصل الى 100 متر (PoE160S)</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>85.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>66.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>40.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>289.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>66.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة | منفذ 1G، PoE+ أو تيار مستمر، محول متضمن، ضمان 5 سنوات، بوابة كابتيف، شبكة، تجوال WPA3، تجربة واي فاي للأعمال</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>364.48 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن TL-POE170S PoE++ (منفذين جيجابت، متوافق مع 802.3af /at/bt، إجمالي الطاقة بقدرة تصل إلى 60 واط، تصميم يثبت على الحائط وسطح المكتب، التوصيل والتشغيل) اسود</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>183.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>66.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>محول مقسم نشط POE من قطعتين، 48 فولت الى 12 فولت، متوافق مع IEEE 802.3af 10/100Mbps حتى 100 متر لكاميرا IP ونقطة الوصول اللاسلكية والهاتف عبر بروتوكول الإنترنت</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>45.4 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>48.49 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك WLAN Access P. 300mb في الهواء الطلق, CPE210 | وصلة لاسلكية طويلة المدى. هوائي اتجاهي عالي الكسب. مثالية للاستخدام في الهواء الطلق. نقل من نقطة إلى نقطة.</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>220.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210 | C310 C320WS TC60 TC70 C211 C110، كاميرا مراقبة داخلية، كابل محول طاقة بديل</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>97.51 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>186.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك نقطة وصول لاسلكية تثبت بالسقف بسرعة 300 ميجابت في الثانية EAP115</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>129.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في | دقة 2.8 كيه، ضوء 509 غرام، شحن فائق 66 واط، قلم ام الجيل الثالث + كيبورد مغناطيسي + ماوس + عبوة عناية الكل في واحد</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>اونر تابلت باد في 9 (11.5 انش، واي فاي) 2024 سعة تخزين 256 جيجا، ذاكرة رام 8 جيجا، اندرويد 15 (رمادي)</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>1799.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>1348.41 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اس اي 11 انش 4+128 جيجا رمادي، شاشة فل فيو وبطارية كبيرة السعة (مجددة)</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>549.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت باد 7، 11.2 انش، 8+128 جيجا، رمادي، بطارية 8850mAh، شحن تيربو 45 واط، هايبر ايه اي (الشاحن غير متضمن)</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>1029.63 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>1289.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>3499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>بطارية محمولة L18C4P90 بجهد 15.36 فولت و46 واط في الساعة و2995mAh متوافقة مع لينوفو ثينك باد L13 الجيل الاول SB10T83121 5B10W13933 5B10W13935</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>223.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>ريلمي باد 2 128 جيجا 6 جيجا انسبايراشن جرين واي فاي RMP2205 EU</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>1026.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 مي، 4GB + 128GB، ازرق سيان، ميديا تيك هيليو G100-الترا، شاشة 11 انش 2.5K 90Hz، بطارية 9000mAh، مع شاحن</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>910.57 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>تشو وي تابلت هاي 10 ماكس 33 سم 2880 × 1920 IPS، معالج انتل N150 (4C/4T، حتى 3.6Ghz)، 12GB DDR5، 512GB SSD، ويندوز 11 باد 3 في 1، واي فاي 6، كيبورد عربي</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>2147.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ون بلس باد 3 سناب دراجون® 8 ايليت معدل تحديث 144 هرتز مع تقنية واي فاي (لون فضي مصنفر، 16+ 512 جيجابايت)</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>5385.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت باد ميني 12GB+512GB - تابلت 8.8 انش 3K 165Hz، الأبعاد 9400+، 7500mAh 67 واط، 13MP+8MP، هايبر او اس، اسود (مع الشاحن متضمن)</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>2682.22 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>تابلت باد 7 11.2 بوصة 8+256 جيجابايت وشاشة 3.2K 144 هرتز، بطارية سناب دراجون 7 +جيل 3 8850 ميلي امبير في الساعة، شحن سريع 45 واط، هايبر ايه اي، 4 مكبرات صوت، تجربة سطح مكتب سلسة وشاحن من شاومي، أخضر</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>1667.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>واقي شاشة من جينكيم لأجهزة شاومي إم آي باد 6/6 برو مصنوع من فيلم بملمس ورقي عدد 2 قطعة بملمس الكتابة على الورق</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>39.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>38.49 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة | 3 Ports for all USB-C/A devices,For all 12-24V Vehicles,Lightweight design,travel-ready,Intelligent safety protection</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>88.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج | fast charge for MacBook&amp;laptops, Charge 3 devices simultaneously,Intelligent safety protection,for long road trips</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج | All-Metal, Intelligent Safety Protection, Mini Type-C Car Charger for iPhone 17 16 Pro Max Samsung S26 S25 Huawei Honor etc</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>35.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>45.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>35.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة | 2 Ports for all USB-C/A devices,For all 12-24V Vehicles,Ideal for daily commute,Smart safety protection</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>49.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>75.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة بقدرة 48 واط مع شحن سريع نوع C ومنفذ USB 3.0 للشحن السريع من موج ماكس، لون أسود</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب | Works seamlessly with iPhone,Samsung,MacBook,and all USB-C/A devices,Charge 3 devices simultaneously,for trip &amp; travel</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب | Cigarette Lighter with 65W Retractable Cable, USB C and USB A Charging Ports, Voltage Display, for iPhone/Android/iPad/Laptop</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>شاحن جوال للسيارة قابل للسحب فائق السرعة بقدرة 120 واط، متوافق مع جوالات ابل ايفون واندرويد</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>37.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -489,7 +489,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-10</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ضمان : 24 شهر</t>
+          <t>اوتلت مكعب</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>5.0 ر.س</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>mokab</t>
+          <t>aletawiksa</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>اوتلت مكعب</t>
+          <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>5.0 ر.س</t>
+          <t>9.0 ر.س</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>اكسسوارات ايفون 18</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>9.0 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
+          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
+          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>9.96 ر.س</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>9.96 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1613,22 +1613,22 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -1833,22 +1833,396 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>149.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>149.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>alwan7</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>50.0 ر.س</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>129.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج | شاحن عالي السعة وآمن للاستخدام أثناء الطيران، يدعم الشحن السريع لثلاثة أجهزة وشاشة عرض رقمية لأجهزة MacBook iPad آيفون 18 برو</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>208.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>99.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>189.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, charges 3 devices at once Compatible with iPhone 18 Pro Max</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>138.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>82.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>139.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة من بي دي بيست مع كابل مدمج، شحن سريع USB نوع سي 22.5 واط | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>99.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000 | حزمة بطارية 20,000 مللي أمبير في الساعة مع كابلات مدمجة مزدوجة، منافذ USB-C وUSB-A لسلسلة ايفون 17 / 16 وجالكسي وماك بوك</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>178.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ | Flight-Approved, digital display, charge 3 devices, ultra-fast charging Compatible with Laptop/MacBook/iPhone 18 Pro/Samsung</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>259.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة 22.5 واط شحن سريع، اصغر من معظم الشواحن 20 كلفن، باور بانك محمول مع كيبل مدمج، 4 مخارج وشاشة LED، مناسب للسفر لاجهزة ايفون وسامسونج والتابلت (ابيض)</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>باور بانك شاومي بقوة 22.5 واط سعة 20000 ميلي امبير في الساعة (كيبل مدمج) لون رمادي فاتح</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -489,7 +489,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-11</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1896,336 +1896,6 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل | ترقية 2025، شحن سريع، متوافق مع سلسلة ايفون 17 / 16 / 15 وجالكسي وغيرها</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية | شحن سريع بقوة 22.5W، 2 USB-A + 1 USB-C، تصميم صغير الحجم مناسب للسفر بالطائرة، بطارية 2000mAh، يشحن هاتف آيفون 17 برو 4.2 مرة</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>129.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج | شاحن عالي السعة وآمن للاستخدام أثناء الطيران، يدعم الشحن السريع لثلاثة أجهزة وشاشة عرض رقمية لأجهزة MacBook iPad آيفون 18 برو</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>208.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>99.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>189.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب | Two‑Way PPS fast charging, LED digital display, flight-safe, charges 3 devices at once Compatible with iPhone 18 Pro Max</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>82.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو | Flight-Safe, Built in USB C Cable, Travel Essential, Battery Phone Pack for iPhone 17 16 Pro Samsung S26 S25 Honor iPad etc</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>139.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من بي دي بيست مع كابل مدمج، شحن سريع USB نوع سي 22.5 واط | Flight-Safe, LED Display, 5 Outputs &amp; 3 Inputs, Charge 6 Devices at Once, Slim &amp; Compact, Compatible with iPhone &amp; Android</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>99.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000 | حزمة بطارية 20,000 مللي أمبير في الساعة مع كابلات مدمجة مزدوجة، منافذ USB-C وUSB-A لسلسلة ايفون 17 / 16 وجالكسي وماك بوك</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>178.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ | Flight-Approved, digital display, charge 3 devices, ultra-fast charging Compatible with Laptop/MacBook/iPhone 18 Pro/Samsung</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>259.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 22.5 واط شحن سريع، اصغر من معظم الشواحن 20 كلفن، باور بانك محمول مع كيبل مدمج، 4 مخارج وشاشة LED، مناسب للسفر لاجهزة ايفون وسامسونج والتابلت (ابيض)</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>باور بانك شاومي بقوة 22.5 واط سعة 20000 ميلي امبير في الساعة (كيبل مدمج) لون رمادي فاتح</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>85.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
